--- a/data/SI/SI_4_Mappings.xlsx
+++ b/data/SI/SI_4_Mappings.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://polymtlca-my.sharepoint.com/personal/marin_pellan_polymtl_ca/Documents/POST_DOC/CODE/regionalized_lci_mineral/data/SI/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="130" documentId="11_AD4D9D64A577C15A4A5418A680D85C6E5BDEDD8E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A8974AA8-14BE-4F32-85D6-BEB5CFFF5F7B}"/>
+  <xr:revisionPtr revIDLastSave="133" documentId="11_AD4D9D64A577C15A4A5418A680D85C6E5BDEDD8E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{62CA22A0-F75E-4920-B443-B28D3F8EE66A}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="1" r:id="rId1"/>
@@ -19,6 +19,10 @@
     <sheet name="biosphere_RI" sheetId="4" r:id="rId4"/>
     <sheet name="technosphere_RI" sheetId="5" r:id="rId5"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">technosphere_EI!$A$1:$I$104</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">technosphere_RI!$A$1:$I$1</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -2425,10 +2429,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2698,13 +2698,13 @@
     <tabColor rgb="FFC00000"/>
   </sheetPr>
   <dimension ref="A1:B7"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="20.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="138.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="138.26953125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2712,7 +2712,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="17.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -2720,7 +2720,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="66.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" ht="64" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -2728,7 +2728,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
@@ -2736,7 +2736,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>8</v>
       </c>
@@ -2744,7 +2744,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>10</v>
       </c>
@@ -2752,7 +2752,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>11</v>
       </c>
@@ -2768,23 +2768,23 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1EE40601-4595-4548-A36C-D886EC233248}">
   <dimension ref="A1:M423"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="20" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="51.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="20.5703125" customWidth="1"/>
-    <col min="5" max="5" width="17.85546875" customWidth="1"/>
-    <col min="6" max="6" width="15.5703125" customWidth="1"/>
-    <col min="7" max="7" width="16.85546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="27.85546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="54.42578125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="41.7109375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="34.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="51.81640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.54296875" customWidth="1"/>
+    <col min="5" max="5" width="17.81640625" customWidth="1"/>
+    <col min="6" max="6" width="15.54296875" customWidth="1"/>
+    <col min="7" max="7" width="16.81640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="27.81640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="54.453125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="41.7265625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.1796875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="34.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" s="5" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
         <v>13</v>
       </c>
@@ -2825,7 +2825,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>26</v>
       </c>
@@ -2860,7 +2860,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>26</v>
       </c>
@@ -2895,7 +2895,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="4" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A4" s="9" t="s">
         <v>26</v>
       </c>
@@ -2933,7 +2933,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>26</v>
       </c>
@@ -2968,7 +2968,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>26</v>
       </c>
@@ -3003,7 +3003,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>26</v>
       </c>
@@ -3038,7 +3038,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>26</v>
       </c>
@@ -3073,7 +3073,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>26</v>
       </c>
@@ -3108,7 +3108,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>26</v>
       </c>
@@ -3143,7 +3143,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>26</v>
       </c>
@@ -3181,7 +3181,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>26</v>
       </c>
@@ -3219,7 +3219,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>26</v>
       </c>
@@ -3257,7 +3257,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>26</v>
       </c>
@@ -3292,7 +3292,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>26</v>
       </c>
@@ -3327,7 +3327,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>26</v>
       </c>
@@ -3362,7 +3362,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>26</v>
       </c>
@@ -3397,7 +3397,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>26</v>
       </c>
@@ -3432,7 +3432,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A19" s="9" t="s">
         <v>26</v>
       </c>
@@ -3469,7 +3469,7 @@
       <c r="L19" s="9"/>
       <c r="M19" s="9"/>
     </row>
-    <row r="20" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A20" s="9" t="s">
         <v>26</v>
       </c>
@@ -3504,7 +3504,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="21" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A21" s="9" t="s">
         <v>26</v>
       </c>
@@ -3539,7 +3539,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="22" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A22" s="9" t="s">
         <v>26</v>
       </c>
@@ -3574,7 +3574,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="23" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A23" s="9" t="s">
         <v>26</v>
       </c>
@@ -3609,7 +3609,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="24" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>26</v>
       </c>
@@ -3646,7 +3646,7 @@
       <c r="L24"/>
       <c r="M24"/>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>26</v>
       </c>
@@ -3681,7 +3681,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>26</v>
       </c>
@@ -3716,7 +3716,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>26</v>
       </c>
@@ -3751,7 +3751,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>26</v>
       </c>
@@ -3786,7 +3786,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>26</v>
       </c>
@@ -3821,7 +3821,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>26</v>
       </c>
@@ -3856,7 +3856,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>26</v>
       </c>
@@ -3891,7 +3891,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>26</v>
       </c>
@@ -3926,7 +3926,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A33" s="9" t="s">
         <v>26</v>
       </c>
@@ -3963,7 +3963,7 @@
       <c r="L33" s="9"/>
       <c r="M33" s="9"/>
     </row>
-    <row r="34" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A34" s="9" t="s">
         <v>26</v>
       </c>
@@ -3998,7 +3998,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="35" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A35" s="9" t="s">
         <v>26</v>
       </c>
@@ -4033,7 +4033,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="36" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A36" s="9" t="s">
         <v>26</v>
       </c>
@@ -4068,7 +4068,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="37" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A37" s="9" t="s">
         <v>26</v>
       </c>
@@ -4103,7 +4103,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="38" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A38" s="9" t="s">
         <v>26</v>
       </c>
@@ -4138,7 +4138,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="39" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A39" s="9" t="s">
         <v>26</v>
       </c>
@@ -4173,7 +4173,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="40" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A40" s="9" t="s">
         <v>26</v>
       </c>
@@ -4208,7 +4208,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="41" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A41" s="9" t="s">
         <v>26</v>
       </c>
@@ -4243,7 +4243,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="42" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>26</v>
       </c>
@@ -4280,7 +4280,7 @@
       <c r="L42"/>
       <c r="M42"/>
     </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>26</v>
       </c>
@@ -4315,7 +4315,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>26</v>
       </c>
@@ -4350,7 +4350,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="45" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>26</v>
       </c>
@@ -4385,7 +4385,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="46" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>26</v>
       </c>
@@ -4420,7 +4420,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="47" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>26</v>
       </c>
@@ -4455,7 +4455,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="48" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>26</v>
       </c>
@@ -4490,7 +4490,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>26</v>
       </c>
@@ -4525,7 +4525,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>26</v>
       </c>
@@ -4560,7 +4560,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>26</v>
       </c>
@@ -4595,7 +4595,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>26</v>
       </c>
@@ -4630,7 +4630,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>26</v>
       </c>
@@ -4665,7 +4665,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>26</v>
       </c>
@@ -4700,7 +4700,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>26</v>
       </c>
@@ -4735,7 +4735,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>26</v>
       </c>
@@ -4770,7 +4770,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>26</v>
       </c>
@@ -4805,7 +4805,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>26</v>
       </c>
@@ -4840,7 +4840,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>26</v>
       </c>
@@ -4875,7 +4875,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>26</v>
       </c>
@@ -4910,7 +4910,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>26</v>
       </c>
@@ -4945,7 +4945,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>26</v>
       </c>
@@ -4980,7 +4980,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>26</v>
       </c>
@@ -5015,7 +5015,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>26</v>
       </c>
@@ -5050,7 +5050,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="65" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>26</v>
       </c>
@@ -5085,7 +5085,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="66" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>26</v>
       </c>
@@ -5120,7 +5120,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="67" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>26</v>
       </c>
@@ -5155,7 +5155,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="68" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>26</v>
       </c>
@@ -5190,7 +5190,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="69" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>26</v>
       </c>
@@ -5225,7 +5225,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="70" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>26</v>
       </c>
@@ -5260,7 +5260,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="71" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>26</v>
       </c>
@@ -5295,7 +5295,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="72" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>26</v>
       </c>
@@ -5330,7 +5330,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="73" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>26</v>
       </c>
@@ -5365,7 +5365,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="74" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>26</v>
       </c>
@@ -5400,7 +5400,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="75" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>26</v>
       </c>
@@ -5435,7 +5435,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="76" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>26</v>
       </c>
@@ -5470,7 +5470,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="77" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
         <v>26</v>
       </c>
@@ -5505,7 +5505,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="78" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
         <v>26</v>
       </c>
@@ -5540,7 +5540,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="79" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
         <v>26</v>
       </c>
@@ -5575,7 +5575,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="80" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A80" s="9" t="s">
         <v>26</v>
       </c>
@@ -5612,7 +5612,7 @@
       <c r="L80" s="9"/>
       <c r="M80" s="9"/>
     </row>
-    <row r="81" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A81" s="9" t="s">
         <v>26</v>
       </c>
@@ -5647,7 +5647,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="82" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A82" s="9" t="s">
         <v>26</v>
       </c>
@@ -5682,7 +5682,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="83" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A83" s="9" t="s">
         <v>26</v>
       </c>
@@ -5717,7 +5717,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="84" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A84" s="9" t="s">
         <v>26</v>
       </c>
@@ -5752,7 +5752,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="85" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A85" s="9" t="s">
         <v>26</v>
       </c>
@@ -5787,7 +5787,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="86" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A86" s="9" t="s">
         <v>26</v>
       </c>
@@ -5822,7 +5822,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="87" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A87" s="9" t="s">
         <v>26</v>
       </c>
@@ -5857,7 +5857,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="88" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
         <v>26</v>
       </c>
@@ -5894,7 +5894,7 @@
       <c r="L88"/>
       <c r="M88"/>
     </row>
-    <row r="89" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
         <v>26</v>
       </c>
@@ -5929,7 +5929,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="90" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
         <v>26</v>
       </c>
@@ -5964,7 +5964,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="91" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
         <v>26</v>
       </c>
@@ -5999,7 +5999,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="92" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
         <v>26</v>
       </c>
@@ -6034,7 +6034,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="93" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
         <v>26</v>
       </c>
@@ -6066,7 +6066,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="94" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
         <v>26</v>
       </c>
@@ -6101,7 +6101,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="95" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
         <v>26</v>
       </c>
@@ -6136,7 +6136,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="96" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
         <v>26</v>
       </c>
@@ -6171,7 +6171,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="97" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
         <v>26</v>
       </c>
@@ -6206,7 +6206,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="98" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
         <v>26</v>
       </c>
@@ -6241,7 +6241,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="99" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
         <v>26</v>
       </c>
@@ -6276,7 +6276,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="100" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
         <v>26</v>
       </c>
@@ -6311,7 +6311,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="101" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
         <v>26</v>
       </c>
@@ -6340,7 +6340,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="102" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
         <v>26</v>
       </c>
@@ -6375,7 +6375,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="103" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
         <v>26</v>
       </c>
@@ -6410,7 +6410,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="104" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
         <v>26</v>
       </c>
@@ -6442,7 +6442,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="105" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
         <v>26</v>
       </c>
@@ -6479,7 +6479,7 @@
       <c r="L105"/>
       <c r="M105"/>
     </row>
-    <row r="106" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A106" s="9" t="s">
         <v>26</v>
       </c>
@@ -6514,7 +6514,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="107" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A107" s="9" t="s">
         <v>26</v>
       </c>
@@ -6549,7 +6549,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="108" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A108" s="9" t="s">
         <v>26</v>
       </c>
@@ -6584,7 +6584,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="109" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A109" s="9" t="s">
         <v>26</v>
       </c>
@@ -6619,7 +6619,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="110" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A110" s="9" t="s">
         <v>26</v>
       </c>
@@ -6654,7 +6654,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="111" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A111" s="9" t="s">
         <v>26</v>
       </c>
@@ -6691,7 +6691,7 @@
       <c r="L111" s="9"/>
       <c r="M111" s="9"/>
     </row>
-    <row r="112" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
         <v>26</v>
       </c>
@@ -6726,7 +6726,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="113" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
         <v>26</v>
       </c>
@@ -6761,7 +6761,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="114" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
         <v>26</v>
       </c>
@@ -6796,7 +6796,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="115" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
         <v>26</v>
       </c>
@@ -6831,7 +6831,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="116" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
         <v>26</v>
       </c>
@@ -6866,7 +6866,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="117" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
         <v>26</v>
       </c>
@@ -6901,7 +6901,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="118" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
         <v>26</v>
       </c>
@@ -6936,7 +6936,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="119" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
         <v>26</v>
       </c>
@@ -6971,7 +6971,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="120" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
         <v>26</v>
       </c>
@@ -7006,7 +7006,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="121" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
         <v>26</v>
       </c>
@@ -7043,7 +7043,7 @@
       <c r="L121"/>
       <c r="M121"/>
     </row>
-    <row r="122" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
         <v>26</v>
       </c>
@@ -7078,7 +7078,7 @@
       <c r="L122"/>
       <c r="M122"/>
     </row>
-    <row r="123" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A123" s="9" t="s">
         <v>26</v>
       </c>
@@ -7113,7 +7113,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="124" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A124" s="9" t="s">
         <v>26</v>
       </c>
@@ -7148,7 +7148,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="125" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A125" s="9" t="s">
         <v>26</v>
       </c>
@@ -7183,7 +7183,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="126" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A126" s="9" t="s">
         <v>26</v>
       </c>
@@ -7218,7 +7218,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="127" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A127" s="9" t="s">
         <v>26</v>
       </c>
@@ -7253,7 +7253,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="128" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A128" s="9" t="s">
         <v>26</v>
       </c>
@@ -7288,7 +7288,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="129" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A129" s="9" t="s">
         <v>26</v>
       </c>
@@ -7323,7 +7323,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="130" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A130" s="9" t="s">
         <v>26</v>
       </c>
@@ -7358,7 +7358,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="131" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A131" s="9" t="s">
         <v>26</v>
       </c>
@@ -7393,7 +7393,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="132" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A132" s="9" t="s">
         <v>26</v>
       </c>
@@ -7428,7 +7428,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="133" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A133" s="9" t="s">
         <v>26</v>
       </c>
@@ -7463,7 +7463,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="134" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A134" s="9" t="s">
         <v>26</v>
       </c>
@@ -7498,7 +7498,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="135" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A135" s="9" t="s">
         <v>26</v>
       </c>
@@ -7535,7 +7535,7 @@
       <c r="L135" s="9"/>
       <c r="M135" s="9"/>
     </row>
-    <row r="136" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A136" s="9" t="s">
         <v>26</v>
       </c>
@@ -7572,7 +7572,7 @@
       <c r="L136" s="9"/>
       <c r="M136" s="9"/>
     </row>
-    <row r="137" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
         <v>26</v>
       </c>
@@ -7607,7 +7607,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="138" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
         <v>26</v>
       </c>
@@ -7642,7 +7642,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="139" spans="1:13" s="11" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:13" s="11" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
         <v>26</v>
       </c>
@@ -7679,7 +7679,7 @@
       <c r="L139"/>
       <c r="M139"/>
     </row>
-    <row r="140" spans="1:13" s="11" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:13" s="11" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
         <v>26</v>
       </c>
@@ -7716,7 +7716,7 @@
       <c r="L140"/>
       <c r="M140"/>
     </row>
-    <row r="141" spans="1:13" s="11" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:13" s="11" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A141" s="11" t="s">
         <v>26</v>
       </c>
@@ -7754,7 +7754,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="142" spans="1:13" s="11" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:13" s="11" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A142" s="11" t="s">
         <v>26</v>
       </c>
@@ -7789,7 +7789,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="143" spans="1:13" s="11" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:13" s="11" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A143" s="11" t="s">
         <v>26</v>
       </c>
@@ -7824,7 +7824,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="144" spans="1:13" s="11" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:13" s="11" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A144" s="11" t="s">
         <v>26</v>
       </c>
@@ -7859,7 +7859,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="145" spans="1:13" s="11" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:13" s="11" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A145" s="11" t="s">
         <v>26</v>
       </c>
@@ -7897,7 +7897,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="146" spans="1:13" s="11" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:13" s="11" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A146" s="11" t="s">
         <v>26</v>
       </c>
@@ -7935,7 +7935,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="147" spans="1:13" s="11" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:13" s="11" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A147" s="11" t="s">
         <v>26</v>
       </c>
@@ -7973,7 +7973,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="148" spans="1:13" s="11" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:13" s="11" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A148" s="11" t="s">
         <v>26</v>
       </c>
@@ -8011,7 +8011,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="149" spans="1:13" s="11" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:13" s="11" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A149" s="11" t="s">
         <v>26</v>
       </c>
@@ -8049,7 +8049,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="150" spans="1:13" s="11" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:13" s="11" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A150" s="11" t="s">
         <v>26</v>
       </c>
@@ -8087,7 +8087,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="151" spans="1:13" s="11" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:13" s="11" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A151" s="11" t="s">
         <v>26</v>
       </c>
@@ -8125,7 +8125,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="152" spans="1:13" s="11" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:13" s="11" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A152" s="11" t="s">
         <v>26</v>
       </c>
@@ -8163,7 +8163,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="153" spans="1:13" s="11" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:13" s="11" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A153" s="11" t="s">
         <v>26</v>
       </c>
@@ -8201,7 +8201,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="154" spans="1:13" s="11" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:13" s="11" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A154" s="11" t="s">
         <v>26</v>
       </c>
@@ -8239,7 +8239,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="155" spans="1:13" s="11" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:13" s="11" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A155" s="11" t="s">
         <v>26</v>
       </c>
@@ -8277,7 +8277,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="156" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A156" s="11" t="s">
         <v>26</v>
       </c>
@@ -8316,7 +8316,7 @@
       </c>
       <c r="M156" s="11"/>
     </row>
-    <row r="157" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A157" s="11" t="s">
         <v>26</v>
       </c>
@@ -8355,7 +8355,7 @@
       </c>
       <c r="M157" s="11"/>
     </row>
-    <row r="158" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A158" t="s">
         <v>26</v>
       </c>
@@ -8390,7 +8390,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="159" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A159" t="s">
         <v>26</v>
       </c>
@@ -8425,7 +8425,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="160" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A160" t="s">
         <v>26</v>
       </c>
@@ -8460,7 +8460,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="161" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A161" t="s">
         <v>26</v>
       </c>
@@ -8495,7 +8495,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="162" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A162" t="s">
         <v>26</v>
       </c>
@@ -8530,7 +8530,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="163" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A163" t="s">
         <v>26</v>
       </c>
@@ -8565,7 +8565,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="164" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A164" t="s">
         <v>26</v>
       </c>
@@ -8600,7 +8600,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="165" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A165" t="s">
         <v>26</v>
       </c>
@@ -8635,7 +8635,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="166" spans="1:13" s="13" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:13" s="13" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A166" t="s">
         <v>26</v>
       </c>
@@ -8672,7 +8672,7 @@
       <c r="L166"/>
       <c r="M166"/>
     </row>
-    <row r="167" spans="1:13" s="13" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:13" s="13" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A167" s="13" t="s">
         <v>26</v>
       </c>
@@ -8710,7 +8710,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="168" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A168" s="13" t="s">
         <v>26</v>
       </c>
@@ -8749,7 +8749,7 @@
       </c>
       <c r="M168" s="13"/>
     </row>
-    <row r="169" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A169" t="s">
         <v>26</v>
       </c>
@@ -8784,7 +8784,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="170" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A170" t="s">
         <v>26</v>
       </c>
@@ -8819,7 +8819,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="171" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A171" t="s">
         <v>26</v>
       </c>
@@ -8854,7 +8854,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="172" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A172" t="s">
         <v>26</v>
       </c>
@@ -8889,7 +8889,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="173" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A173" t="s">
         <v>26</v>
       </c>
@@ -8924,7 +8924,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="174" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A174" t="s">
         <v>26</v>
       </c>
@@ -8959,7 +8959,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="175" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A175" t="s">
         <v>26</v>
       </c>
@@ -8994,7 +8994,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="176" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A176" t="s">
         <v>26</v>
       </c>
@@ -9029,7 +9029,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="177" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A177" t="s">
         <v>26</v>
       </c>
@@ -9064,7 +9064,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="178" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A178" t="s">
         <v>26</v>
       </c>
@@ -9099,7 +9099,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="179" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A179" t="s">
         <v>26</v>
       </c>
@@ -9134,7 +9134,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="180" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A180" t="s">
         <v>26</v>
       </c>
@@ -9169,7 +9169,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="181" spans="1:13" s="11" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:13" s="11" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A181" t="s">
         <v>26</v>
       </c>
@@ -9206,7 +9206,7 @@
       <c r="L181"/>
       <c r="M181"/>
     </row>
-    <row r="182" spans="1:13" s="11" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:13" s="11" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A182" s="11" t="s">
         <v>26</v>
       </c>
@@ -9241,7 +9241,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="183" spans="1:13" s="11" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:13" s="11" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A183" s="11" t="s">
         <v>26</v>
       </c>
@@ -9276,7 +9276,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="184" spans="1:13" s="11" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:13" s="11" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A184" s="11" t="s">
         <v>26</v>
       </c>
@@ -9311,7 +9311,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="185" spans="1:13" s="11" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:13" s="11" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A185" s="11" t="s">
         <v>26</v>
       </c>
@@ -9346,7 +9346,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="186" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A186" s="11" t="s">
         <v>26</v>
       </c>
@@ -9383,7 +9383,7 @@
       <c r="L186" s="11"/>
       <c r="M186" s="11"/>
     </row>
-    <row r="187" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A187" t="s">
         <v>26</v>
       </c>
@@ -9418,7 +9418,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="188" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A188" t="s">
         <v>26</v>
       </c>
@@ -9453,7 +9453,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="189" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A189" t="s">
         <v>26</v>
       </c>
@@ -9488,7 +9488,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="190" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A190" t="s">
         <v>26</v>
       </c>
@@ -9523,7 +9523,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="191" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A191" t="s">
         <v>26</v>
       </c>
@@ -9558,7 +9558,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="192" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A192" t="s">
         <v>26</v>
       </c>
@@ -9593,7 +9593,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="193" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A193" t="s">
         <v>26</v>
       </c>
@@ -9628,7 +9628,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="194" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A194" t="s">
         <v>26</v>
       </c>
@@ -9663,7 +9663,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="195" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A195" t="s">
         <v>26</v>
       </c>
@@ -9698,7 +9698,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="196" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A196" t="s">
         <v>26</v>
       </c>
@@ -9733,7 +9733,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="197" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A197" t="s">
         <v>26</v>
       </c>
@@ -9768,7 +9768,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="198" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A198" t="s">
         <v>26</v>
       </c>
@@ -9803,7 +9803,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="199" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A199" t="s">
         <v>26</v>
       </c>
@@ -9838,7 +9838,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="200" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A200" t="s">
         <v>26</v>
       </c>
@@ -9873,7 +9873,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="201" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A201" t="s">
         <v>26</v>
       </c>
@@ -9908,7 +9908,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="202" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A202" t="s">
         <v>26</v>
       </c>
@@ -9943,7 +9943,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="203" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A203" t="s">
         <v>26</v>
       </c>
@@ -9978,7 +9978,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="204" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A204" t="s">
         <v>26</v>
       </c>
@@ -10013,7 +10013,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="205" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A205" t="s">
         <v>26</v>
       </c>
@@ -10048,7 +10048,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="206" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A206" t="s">
         <v>26</v>
       </c>
@@ -10083,7 +10083,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="207" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A207" t="s">
         <v>26</v>
       </c>
@@ -10118,7 +10118,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="208" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A208" t="s">
         <v>26</v>
       </c>
@@ -10153,7 +10153,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="209" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A209" t="s">
         <v>26</v>
       </c>
@@ -10188,7 +10188,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="210" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A210" t="s">
         <v>26</v>
       </c>
@@ -10223,7 +10223,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="211" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A211" t="s">
         <v>26</v>
       </c>
@@ -10258,7 +10258,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="212" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A212" t="s">
         <v>26</v>
       </c>
@@ -10293,7 +10293,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="213" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A213" t="s">
         <v>26</v>
       </c>
@@ -10328,7 +10328,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="214" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A214" t="s">
         <v>26</v>
       </c>
@@ -10363,7 +10363,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="215" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A215" t="s">
         <v>26</v>
       </c>
@@ -10400,7 +10400,7 @@
       <c r="L215"/>
       <c r="M215"/>
     </row>
-    <row r="216" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A216" s="9" t="s">
         <v>26</v>
       </c>
@@ -10435,7 +10435,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="217" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A217" s="9" t="s">
         <v>26</v>
       </c>
@@ -10470,7 +10470,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="218" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A218" s="9" t="s">
         <v>26</v>
       </c>
@@ -10505,7 +10505,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="219" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A219" s="9" t="s">
         <v>26</v>
       </c>
@@ -10540,7 +10540,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="220" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A220" s="9" t="s">
         <v>26</v>
       </c>
@@ -10575,7 +10575,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="221" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A221" s="9" t="s">
         <v>26</v>
       </c>
@@ -10610,7 +10610,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="222" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A222" s="9" t="s">
         <v>26</v>
       </c>
@@ -10645,7 +10645,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="223" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A223" s="9" t="s">
         <v>26</v>
       </c>
@@ -10680,7 +10680,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="224" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A224" s="9" t="s">
         <v>26</v>
       </c>
@@ -10717,7 +10717,7 @@
       <c r="L224" s="9"/>
       <c r="M224" s="9"/>
     </row>
-    <row r="225" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A225" t="s">
         <v>26</v>
       </c>
@@ -10752,7 +10752,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="226" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A226" t="s">
         <v>26</v>
       </c>
@@ -10787,7 +10787,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="227" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A227" t="s">
         <v>26</v>
       </c>
@@ -10822,7 +10822,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="228" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A228" t="s">
         <v>26</v>
       </c>
@@ -10857,7 +10857,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="229" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A229" t="s">
         <v>26</v>
       </c>
@@ -10892,7 +10892,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="230" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A230" t="s">
         <v>26</v>
       </c>
@@ -10927,7 +10927,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="231" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A231" t="s">
         <v>26</v>
       </c>
@@ -10962,7 +10962,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="232" spans="1:13" s="11" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:13" s="11" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A232" t="s">
         <v>26</v>
       </c>
@@ -10999,7 +10999,7 @@
       <c r="L232"/>
       <c r="M232"/>
     </row>
-    <row r="233" spans="1:13" s="11" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:13" s="11" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A233" s="11" t="s">
         <v>26</v>
       </c>
@@ -11037,7 +11037,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="234" spans="1:13" s="11" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:13" s="11" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A234" s="11" t="s">
         <v>26</v>
       </c>
@@ -11075,7 +11075,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="235" spans="1:13" s="11" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:13" s="11" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A235" s="11" t="s">
         <v>26</v>
       </c>
@@ -11113,7 +11113,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="236" spans="1:13" s="11" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:13" s="11" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A236" s="11" t="s">
         <v>26</v>
       </c>
@@ -11151,7 +11151,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="237" spans="1:13" s="11" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:13" s="11" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A237" s="11" t="s">
         <v>26</v>
       </c>
@@ -11189,7 +11189,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="238" spans="1:13" s="11" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:13" s="11" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A238" s="11" t="s">
         <v>26</v>
       </c>
@@ -11224,7 +11224,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="239" spans="1:13" s="11" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:13" s="11" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A239" s="11" t="s">
         <v>26</v>
       </c>
@@ -11259,7 +11259,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="240" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A240" s="11" t="s">
         <v>26</v>
       </c>
@@ -11296,7 +11296,7 @@
       <c r="L240" s="11"/>
       <c r="M240" s="11"/>
     </row>
-    <row r="241" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A241" t="s">
         <v>26</v>
       </c>
@@ -11331,7 +11331,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="242" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A242" t="s">
         <v>26</v>
       </c>
@@ -11366,7 +11366,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="243" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A243" t="s">
         <v>26</v>
       </c>
@@ -11401,7 +11401,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="244" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A244" t="s">
         <v>26</v>
       </c>
@@ -11436,7 +11436,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="245" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A245" t="s">
         <v>26</v>
       </c>
@@ -11471,7 +11471,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="246" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A246" t="s">
         <v>26</v>
       </c>
@@ -11506,7 +11506,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="247" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A247" t="s">
         <v>26</v>
       </c>
@@ -11541,7 +11541,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="248" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A248" t="s">
         <v>26</v>
       </c>
@@ -11578,7 +11578,7 @@
       <c r="L248"/>
       <c r="M248"/>
     </row>
-    <row r="249" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A249" s="9" t="s">
         <v>26</v>
       </c>
@@ -11613,7 +11613,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="250" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A250" s="9" t="s">
         <v>26</v>
       </c>
@@ -11648,7 +11648,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="251" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A251" s="9" t="s">
         <v>26</v>
       </c>
@@ -11683,7 +11683,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="252" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A252" s="9" t="s">
         <v>26</v>
       </c>
@@ -11718,7 +11718,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="253" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A253" s="9" t="s">
         <v>26</v>
       </c>
@@ -11753,7 +11753,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="254" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A254" s="9" t="s">
         <v>26</v>
       </c>
@@ -11788,7 +11788,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="255" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A255" s="9" t="s">
         <v>26</v>
       </c>
@@ -11823,7 +11823,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="256" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A256" s="9" t="s">
         <v>26</v>
       </c>
@@ -11860,7 +11860,7 @@
       <c r="L256" s="9"/>
       <c r="M256" s="9"/>
     </row>
-    <row r="257" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A257" t="s">
         <v>26</v>
       </c>
@@ -11892,7 +11892,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="258" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A258" t="s">
         <v>26</v>
       </c>
@@ -11927,7 +11927,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="259" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A259" t="s">
         <v>26</v>
       </c>
@@ -11962,7 +11962,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="260" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A260" t="s">
         <v>26</v>
       </c>
@@ -11997,7 +11997,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="261" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A261" t="s">
         <v>26</v>
       </c>
@@ -12029,7 +12029,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="262" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A262" t="s">
         <v>26</v>
       </c>
@@ -12064,7 +12064,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="263" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A263" t="s">
         <v>26</v>
       </c>
@@ -12099,7 +12099,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="264" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A264" t="s">
         <v>26</v>
       </c>
@@ -12134,7 +12134,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="265" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A265" t="s">
         <v>26</v>
       </c>
@@ -12169,7 +12169,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="266" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A266" t="s">
         <v>26</v>
       </c>
@@ -12204,7 +12204,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="267" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A267" t="s">
         <v>26</v>
       </c>
@@ -12239,7 +12239,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="268" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A268" t="s">
         <v>26</v>
       </c>
@@ -12276,7 +12276,7 @@
       <c r="L268"/>
       <c r="M268"/>
     </row>
-    <row r="269" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A269" t="s">
         <v>26</v>
       </c>
@@ -12313,7 +12313,7 @@
       <c r="L269"/>
       <c r="M269"/>
     </row>
-    <row r="270" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A270" s="9" t="s">
         <v>26</v>
       </c>
@@ -12348,7 +12348,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="271" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A271" s="9" t="s">
         <v>26</v>
       </c>
@@ -12383,7 +12383,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="272" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A272" s="9" t="s">
         <v>26</v>
       </c>
@@ -12418,7 +12418,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="273" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A273" s="9" t="s">
         <v>26</v>
       </c>
@@ -12453,7 +12453,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="274" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A274" s="9" t="s">
         <v>26</v>
       </c>
@@ -12490,7 +12490,7 @@
       <c r="L274" s="9"/>
       <c r="M274" s="9"/>
     </row>
-    <row r="275" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A275" s="9" t="s">
         <v>26</v>
       </c>
@@ -12527,7 +12527,7 @@
       <c r="L275" s="9"/>
       <c r="M275" s="9"/>
     </row>
-    <row r="276" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A276" t="s">
         <v>26</v>
       </c>
@@ -12562,7 +12562,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="277" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A277" t="s">
         <v>26</v>
       </c>
@@ -12597,7 +12597,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="278" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A278" t="s">
         <v>26</v>
       </c>
@@ -12632,7 +12632,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="279" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A279" t="s">
         <v>26</v>
       </c>
@@ -12670,7 +12670,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="280" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A280" t="s">
         <v>26</v>
       </c>
@@ -12705,7 +12705,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="281" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A281" t="s">
         <v>26</v>
       </c>
@@ -12740,7 +12740,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="282" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A282" t="s">
         <v>26</v>
       </c>
@@ -12775,7 +12775,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="283" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A283" t="s">
         <v>26</v>
       </c>
@@ -12810,7 +12810,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="284" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A284" t="s">
         <v>26</v>
       </c>
@@ -12845,7 +12845,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="285" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A285" t="s">
         <v>26</v>
       </c>
@@ -12877,7 +12877,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="286" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A286" t="s">
         <v>26</v>
       </c>
@@ -12912,7 +12912,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="287" spans="1:13" s="17" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:13" s="17" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A287" t="s">
         <v>26</v>
       </c>
@@ -12949,7 +12949,7 @@
       <c r="L287"/>
       <c r="M287"/>
     </row>
-    <row r="288" spans="1:13" s="17" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:13" s="17" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A288" t="s">
         <v>26</v>
       </c>
@@ -12982,7 +12982,7 @@
       <c r="L288"/>
       <c r="M288"/>
     </row>
-    <row r="289" spans="1:13" s="17" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:13" s="17" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A289" t="s">
         <v>26</v>
       </c>
@@ -13015,7 +13015,7 @@
       <c r="L289"/>
       <c r="M289"/>
     </row>
-    <row r="290" spans="1:13" s="17" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:13" s="17" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A290" t="s">
         <v>26</v>
       </c>
@@ -13054,7 +13054,7 @@
       </c>
       <c r="M290"/>
     </row>
-    <row r="291" spans="1:13" s="17" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:13" s="17" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A291" t="s">
         <v>26</v>
       </c>
@@ -13093,7 +13093,7 @@
       </c>
       <c r="M291"/>
     </row>
-    <row r="292" spans="1:13" s="13" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:13" s="13" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A292" s="17" t="s">
         <v>26</v>
       </c>
@@ -13132,7 +13132,7 @@
       </c>
       <c r="M292" s="17"/>
     </row>
-    <row r="293" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A293" s="17" t="s">
         <v>26</v>
       </c>
@@ -13171,7 +13171,7 @@
       </c>
       <c r="M293" s="17"/>
     </row>
-    <row r="294" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A294" s="17" t="s">
         <v>26</v>
       </c>
@@ -13210,7 +13210,7 @@
       </c>
       <c r="M294" s="17"/>
     </row>
-    <row r="295" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A295" s="17" t="s">
         <v>26</v>
       </c>
@@ -13249,7 +13249,7 @@
       </c>
       <c r="M295" s="17"/>
     </row>
-    <row r="296" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A296" s="17" t="s">
         <v>26</v>
       </c>
@@ -13288,7 +13288,7 @@
       </c>
       <c r="M296" s="17"/>
     </row>
-    <row r="297" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A297" t="s">
         <v>26</v>
       </c>
@@ -13323,7 +13323,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="298" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A298" t="s">
         <v>26</v>
       </c>
@@ -13358,7 +13358,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="299" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A299" t="s">
         <v>26</v>
       </c>
@@ -13393,7 +13393,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="300" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A300" t="s">
         <v>26</v>
       </c>
@@ -13428,7 +13428,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="301" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A301" t="s">
         <v>26</v>
       </c>
@@ -13463,7 +13463,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="302" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A302" t="s">
         <v>26</v>
       </c>
@@ -13498,7 +13498,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="303" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A303" t="s">
         <v>26</v>
       </c>
@@ -13533,7 +13533,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="304" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A304" t="s">
         <v>26</v>
       </c>
@@ -13568,7 +13568,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="305" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A305" t="s">
         <v>26</v>
       </c>
@@ -13603,7 +13603,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="306" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A306" t="s">
         <v>26</v>
       </c>
@@ -13641,7 +13641,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="307" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A307" t="s">
         <v>26</v>
       </c>
@@ -13679,7 +13679,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="308" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A308" t="s">
         <v>26</v>
       </c>
@@ -13717,7 +13717,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="309" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A309" t="s">
         <v>26</v>
       </c>
@@ -13755,7 +13755,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="310" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A310" t="s">
         <v>26</v>
       </c>
@@ -13790,7 +13790,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="311" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A311" t="s">
         <v>26</v>
       </c>
@@ -13825,7 +13825,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="312" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A312" t="s">
         <v>26</v>
       </c>
@@ -13860,7 +13860,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="313" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A313" t="s">
         <v>26</v>
       </c>
@@ -13895,7 +13895,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="314" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A314" t="s">
         <v>26</v>
       </c>
@@ -13930,7 +13930,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="315" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A315" t="s">
         <v>26</v>
       </c>
@@ -13965,7 +13965,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="316" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A316" t="s">
         <v>26</v>
       </c>
@@ -14000,7 +14000,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="317" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A317" t="s">
         <v>26</v>
       </c>
@@ -14038,7 +14038,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="318" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A318" t="s">
         <v>26</v>
       </c>
@@ -14076,7 +14076,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="319" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A319" t="s">
         <v>26</v>
       </c>
@@ -14114,7 +14114,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="320" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A320" t="s">
         <v>26</v>
       </c>
@@ -14152,7 +14152,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="321" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A321" t="s">
         <v>26</v>
       </c>
@@ -14190,7 +14190,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="322" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A322" t="s">
         <v>26</v>
       </c>
@@ -14228,7 +14228,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="323" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A323" t="s">
         <v>26</v>
       </c>
@@ -14263,7 +14263,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="324" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A324" t="s">
         <v>26</v>
       </c>
@@ -14298,7 +14298,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="325" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A325" t="s">
         <v>26</v>
       </c>
@@ -14333,7 +14333,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="326" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A326" t="s">
         <v>26</v>
       </c>
@@ -14368,7 +14368,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="327" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A327" t="s">
         <v>26</v>
       </c>
@@ -14403,7 +14403,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="328" spans="1:13" s="13" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:13" s="13" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A328" t="s">
         <v>26</v>
       </c>
@@ -14440,7 +14440,7 @@
       <c r="L328"/>
       <c r="M328"/>
     </row>
-    <row r="329" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A329" t="s">
         <v>26</v>
       </c>
@@ -14475,7 +14475,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="330" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A330" s="13" t="s">
         <v>26</v>
       </c>
@@ -14504,7 +14504,7 @@
       <c r="L330" s="13"/>
       <c r="M330" s="13"/>
     </row>
-    <row r="331" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A331" t="s">
         <v>26</v>
       </c>
@@ -14539,7 +14539,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="332" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A332" t="s">
         <v>26</v>
       </c>
@@ -14574,7 +14574,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="333" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A333" t="s">
         <v>26</v>
       </c>
@@ -14609,7 +14609,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="334" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A334" t="s">
         <v>26</v>
       </c>
@@ -14644,7 +14644,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="335" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A335" t="s">
         <v>26</v>
       </c>
@@ -14679,7 +14679,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="336" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A336" t="s">
         <v>26</v>
       </c>
@@ -14714,7 +14714,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="337" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A337" t="s">
         <v>26</v>
       </c>
@@ -14749,7 +14749,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="338" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A338" t="s">
         <v>26</v>
       </c>
@@ -14786,7 +14786,7 @@
       <c r="L338"/>
       <c r="M338"/>
     </row>
-    <row r="339" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A339" t="s">
         <v>26</v>
       </c>
@@ -14823,7 +14823,7 @@
       <c r="L339"/>
       <c r="M339"/>
     </row>
-    <row r="340" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A340" s="9" t="s">
         <v>26</v>
       </c>
@@ -14858,7 +14858,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="341" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A341" s="9" t="s">
         <v>26</v>
       </c>
@@ -14893,7 +14893,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="342" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A342" s="9" t="s">
         <v>26</v>
       </c>
@@ -14928,7 +14928,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="343" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A343" s="9" t="s">
         <v>26</v>
       </c>
@@ -14963,7 +14963,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="344" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A344" s="9" t="s">
         <v>26</v>
       </c>
@@ -14998,7 +14998,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="345" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A345" s="9" t="s">
         <v>26</v>
       </c>
@@ -15033,7 +15033,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="346" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A346" s="9" t="s">
         <v>26</v>
       </c>
@@ -15068,7 +15068,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="347" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A347" s="9" t="s">
         <v>26</v>
       </c>
@@ -15103,7 +15103,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="348" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A348" s="9" t="s">
         <v>26</v>
       </c>
@@ -15138,7 +15138,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="349" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A349" s="9" t="s">
         <v>26</v>
       </c>
@@ -15173,7 +15173,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="350" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A350" s="9" t="s">
         <v>26</v>
       </c>
@@ -15208,7 +15208,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="351" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A351" s="9" t="s">
         <v>26</v>
       </c>
@@ -15245,7 +15245,7 @@
       <c r="L351" s="9"/>
       <c r="M351" s="9"/>
     </row>
-    <row r="352" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A352" s="9" t="s">
         <v>26</v>
       </c>
@@ -15282,7 +15282,7 @@
       <c r="L352" s="9"/>
       <c r="M352" s="9"/>
     </row>
-    <row r="353" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A353" t="s">
         <v>26</v>
       </c>
@@ -15317,7 +15317,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="354" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A354" t="s">
         <v>26</v>
       </c>
@@ -15352,7 +15352,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="355" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A355" t="s">
         <v>26</v>
       </c>
@@ -15385,7 +15385,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="356" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A356" t="s">
         <v>26</v>
       </c>
@@ -15418,7 +15418,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="357" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A357" t="s">
         <v>26</v>
       </c>
@@ -15451,7 +15451,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="358" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A358" t="s">
         <v>26</v>
       </c>
@@ -15484,7 +15484,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="359" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A359" t="s">
         <v>26</v>
       </c>
@@ -15517,7 +15517,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="360" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A360" t="s">
         <v>26</v>
       </c>
@@ -15552,7 +15552,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="361" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A361" t="s">
         <v>26</v>
       </c>
@@ -15587,7 +15587,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="362" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A362" t="s">
         <v>26</v>
       </c>
@@ -15622,7 +15622,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="363" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A363" t="s">
         <v>26</v>
       </c>
@@ -15660,7 +15660,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="364" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A364" t="s">
         <v>26</v>
       </c>
@@ -15698,7 +15698,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="365" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A365" t="s">
         <v>26</v>
       </c>
@@ -15736,7 +15736,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="366" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A366" t="s">
         <v>26</v>
       </c>
@@ -15774,7 +15774,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="367" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A367" t="s">
         <v>26</v>
       </c>
@@ -15812,7 +15812,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="368" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A368" t="s">
         <v>26</v>
       </c>
@@ -15851,7 +15851,7 @@
       </c>
       <c r="M368"/>
     </row>
-    <row r="369" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A369" t="s">
         <v>26</v>
       </c>
@@ -15890,7 +15890,7 @@
       </c>
       <c r="M369"/>
     </row>
-    <row r="370" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A370" t="s">
         <v>26</v>
       </c>
@@ -15927,7 +15927,7 @@
       <c r="L370"/>
       <c r="M370"/>
     </row>
-    <row r="371" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A371" s="9" t="s">
         <v>26</v>
       </c>
@@ -15962,7 +15962,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="372" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A372" s="9" t="s">
         <v>26</v>
       </c>
@@ -15997,7 +15997,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="373" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A373" s="9" t="s">
         <v>26</v>
       </c>
@@ -16032,7 +16032,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="374" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A374" s="9" t="s">
         <v>26</v>
       </c>
@@ -16069,7 +16069,7 @@
       <c r="L374" s="9"/>
       <c r="M374" s="9"/>
     </row>
-    <row r="375" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A375" s="9" t="s">
         <v>26</v>
       </c>
@@ -16106,7 +16106,7 @@
       <c r="L375" s="9"/>
       <c r="M375" s="9"/>
     </row>
-    <row r="376" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A376" s="9" t="s">
         <v>26</v>
       </c>
@@ -16143,7 +16143,7 @@
       <c r="L376" s="9"/>
       <c r="M376" s="9"/>
     </row>
-    <row r="377" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A377" t="s">
         <v>26</v>
       </c>
@@ -16178,7 +16178,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="378" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A378" t="s">
         <v>26</v>
       </c>
@@ -16213,7 +16213,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="379" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A379" t="s">
         <v>26</v>
       </c>
@@ -16248,7 +16248,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="380" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A380" t="s">
         <v>26</v>
       </c>
@@ -16283,7 +16283,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="381" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A381" t="s">
         <v>26</v>
       </c>
@@ -16318,7 +16318,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="382" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A382" t="s">
         <v>26</v>
       </c>
@@ -16353,7 +16353,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="383" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A383" t="s">
         <v>26</v>
       </c>
@@ -16388,7 +16388,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="384" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A384" t="s">
         <v>26</v>
       </c>
@@ -16423,7 +16423,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="385" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A385" t="s">
         <v>26</v>
       </c>
@@ -16458,7 +16458,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="386" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A386" t="s">
         <v>26</v>
       </c>
@@ -16493,7 +16493,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="387" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A387" t="s">
         <v>26</v>
       </c>
@@ -16530,7 +16530,7 @@
       <c r="L387"/>
       <c r="M387"/>
     </row>
-    <row r="388" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A388" t="s">
         <v>26</v>
       </c>
@@ -16567,7 +16567,7 @@
       <c r="L388"/>
       <c r="M388"/>
     </row>
-    <row r="389" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A389" t="s">
         <v>26</v>
       </c>
@@ -16600,7 +16600,7 @@
       <c r="L389"/>
       <c r="M389"/>
     </row>
-    <row r="390" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A390" t="s">
         <v>26</v>
       </c>
@@ -16633,7 +16633,7 @@
       <c r="L390"/>
       <c r="M390"/>
     </row>
-    <row r="391" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A391" t="s">
         <v>26</v>
       </c>
@@ -16666,7 +16666,7 @@
       <c r="L391"/>
       <c r="M391"/>
     </row>
-    <row r="392" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A392" t="s">
         <v>26</v>
       </c>
@@ -16695,7 +16695,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="393" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A393" t="s">
         <v>26</v>
       </c>
@@ -16724,7 +16724,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="394" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A394" t="s">
         <v>26</v>
       </c>
@@ -16753,7 +16753,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="395" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A395" t="s">
         <v>26</v>
       </c>
@@ -16782,7 +16782,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="396" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A396" t="s">
         <v>26</v>
       </c>
@@ -16811,7 +16811,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="397" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A397" t="s">
         <v>26</v>
       </c>
@@ -16840,7 +16840,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="398" spans="1:13" s="15" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:13" s="15" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A398" t="s">
         <v>26</v>
       </c>
@@ -16873,7 +16873,7 @@
       <c r="L398"/>
       <c r="M398"/>
     </row>
-    <row r="399" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A399" t="s">
         <v>26</v>
       </c>
@@ -16906,7 +16906,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="400" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A400" s="9" t="s">
         <v>26</v>
       </c>
@@ -16943,7 +16943,7 @@
       <c r="L400" s="9"/>
       <c r="M400" s="9"/>
     </row>
-    <row r="401" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A401" s="9" t="s">
         <v>26</v>
       </c>
@@ -16980,7 +16980,7 @@
       <c r="L401" s="9"/>
       <c r="M401" s="9"/>
     </row>
-    <row r="402" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A402" s="9" t="s">
         <v>26</v>
       </c>
@@ -17015,7 +17015,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="403" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A403" s="9" t="s">
         <v>26</v>
       </c>
@@ -17050,7 +17050,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="404" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A404" s="9" t="s">
         <v>26</v>
       </c>
@@ -17085,7 +17085,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="405" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A405" s="15" t="s">
         <v>26</v>
       </c>
@@ -17124,7 +17124,7 @@
       </c>
       <c r="M405" s="15"/>
     </row>
-    <row r="406" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A406" s="15" t="s">
         <v>26</v>
       </c>
@@ -17163,7 +17163,7 @@
       </c>
       <c r="M406" s="15"/>
     </row>
-    <row r="407" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A407" s="15" t="s">
         <v>26</v>
       </c>
@@ -17202,7 +17202,7 @@
       </c>
       <c r="M407" s="15"/>
     </row>
-    <row r="408" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A408" s="15" t="s">
         <v>26</v>
       </c>
@@ -17241,7 +17241,7 @@
       </c>
       <c r="M408" s="15"/>
     </row>
-    <row r="409" spans="1:13" s="19" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:13" s="19" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A409" s="15" t="s">
         <v>26</v>
       </c>
@@ -17280,7 +17280,7 @@
       </c>
       <c r="M409" s="15"/>
     </row>
-    <row r="410" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A410" s="15" t="s">
         <v>26</v>
       </c>
@@ -17319,7 +17319,7 @@
       </c>
       <c r="M410" s="15"/>
     </row>
-    <row r="411" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A411" t="s">
         <v>26</v>
       </c>
@@ -17354,7 +17354,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="412" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A412" t="s">
         <v>26</v>
       </c>
@@ -17389,7 +17389,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="413" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A413" t="s">
         <v>26</v>
       </c>
@@ -17424,7 +17424,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="414" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A414" t="s">
         <v>26</v>
       </c>
@@ -17459,7 +17459,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="415" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A415" t="s">
         <v>26</v>
       </c>
@@ -17494,7 +17494,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="416" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A416" s="9" t="s">
         <v>26</v>
       </c>
@@ -17531,7 +17531,7 @@
       <c r="L416" s="9"/>
       <c r="M416" s="9"/>
     </row>
-    <row r="417" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A417" s="9" t="s">
         <v>26</v>
       </c>
@@ -17568,7 +17568,7 @@
       <c r="L417" s="9"/>
       <c r="M417" s="9"/>
     </row>
-    <row r="418" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A418" s="9" t="s">
         <v>26</v>
       </c>
@@ -17605,7 +17605,7 @@
       <c r="L418" s="9"/>
       <c r="M418" s="9"/>
     </row>
-    <row r="419" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A419" s="9" t="s">
         <v>26</v>
       </c>
@@ -17642,7 +17642,7 @@
       <c r="L419" s="9"/>
       <c r="M419" s="9"/>
     </row>
-    <row r="420" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A420" s="9" t="s">
         <v>26</v>
       </c>
@@ -17679,7 +17679,7 @@
       <c r="L420" s="9"/>
       <c r="M420" s="9"/>
     </row>
-    <row r="421" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A421" s="9" t="s">
         <v>26</v>
       </c>
@@ -17716,7 +17716,7 @@
       <c r="L421" s="9"/>
       <c r="M421" s="9"/>
     </row>
-    <row r="422" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A422" s="9" t="s">
         <v>26</v>
       </c>
@@ -17753,7 +17753,7 @@
       <c r="L422" s="9"/>
       <c r="M422" s="9"/>
     </row>
-    <row r="423" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A423" s="9" t="s">
         <v>26</v>
       </c>
@@ -17797,21 +17797,22 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA6C973F-831A-4595-ADBE-42068492B51B}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:I104"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="8.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="46.140625" style="21" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.28515625" style="8" customWidth="1"/>
-    <col min="4" max="4" width="32.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="48.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="69.85546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="46.1796875" style="21" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.26953125" style="8" customWidth="1"/>
+    <col min="4" max="4" width="32.1796875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="48.54296875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="69.81640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.81640625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="12" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="77.85546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="77.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
         <v>13</v>
       </c>
@@ -17840,7 +17841,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>362</v>
       </c>
@@ -17866,7 +17867,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>362</v>
       </c>
@@ -17892,7 +17893,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>362</v>
       </c>
@@ -17921,7 +17922,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>362</v>
       </c>
@@ -17947,7 +17948,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>362</v>
       </c>
@@ -17976,7 +17977,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>394</v>
       </c>
@@ -18005,7 +18006,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>362</v>
       </c>
@@ -18031,7 +18032,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>362</v>
       </c>
@@ -18060,7 +18061,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>362</v>
       </c>
@@ -18089,7 +18090,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>362</v>
       </c>
@@ -18118,7 +18119,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>362</v>
       </c>
@@ -18147,7 +18148,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>362</v>
       </c>
@@ -18176,7 +18177,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>362</v>
       </c>
@@ -18205,7 +18206,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>362</v>
       </c>
@@ -18231,7 +18232,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>362</v>
       </c>
@@ -18257,7 +18258,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>394</v>
       </c>
@@ -18283,7 +18284,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>394</v>
       </c>
@@ -18309,7 +18310,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>394</v>
       </c>
@@ -18335,7 +18336,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>394</v>
       </c>
@@ -18361,7 +18362,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>394</v>
       </c>
@@ -18387,7 +18388,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>394</v>
       </c>
@@ -18416,7 +18417,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>394</v>
       </c>
@@ -18445,7 +18446,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>394</v>
       </c>
@@ -18474,7 +18475,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>394</v>
       </c>
@@ -18503,7 +18504,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>394</v>
       </c>
@@ -18529,7 +18530,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>362</v>
       </c>
@@ -18558,7 +18559,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>394</v>
       </c>
@@ -18587,7 +18588,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>362</v>
       </c>
@@ -18616,7 +18617,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>394</v>
       </c>
@@ -18642,7 +18643,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>394</v>
       </c>
@@ -18668,7 +18669,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>394</v>
       </c>
@@ -18694,7 +18695,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>394</v>
       </c>
@@ -18720,7 +18721,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>394</v>
       </c>
@@ -18746,7 +18747,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>394</v>
       </c>
@@ -18772,7 +18773,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>394</v>
       </c>
@@ -18798,7 +18799,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>362</v>
       </c>
@@ -18827,7 +18828,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>362</v>
       </c>
@@ -18853,7 +18854,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>362</v>
       </c>
@@ -18882,7 +18883,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>362</v>
       </c>
@@ -18911,7 +18912,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>362</v>
       </c>
@@ -18940,7 +18941,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>362</v>
       </c>
@@ -18969,7 +18970,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>362</v>
       </c>
@@ -18998,7 +18999,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>362</v>
       </c>
@@ -19027,7 +19028,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>394</v>
       </c>
@@ -19056,7 +19057,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>362</v>
       </c>
@@ -19085,7 +19086,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>362</v>
       </c>
@@ -19114,7 +19115,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>362</v>
       </c>
@@ -19140,7 +19141,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>394</v>
       </c>
@@ -19166,7 +19167,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>394</v>
       </c>
@@ -19192,7 +19193,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>394</v>
       </c>
@@ -19218,7 +19219,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>362</v>
       </c>
@@ -19247,7 +19248,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>394</v>
       </c>
@@ -19273,7 +19274,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>394</v>
       </c>
@@ -19299,7 +19300,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>362</v>
       </c>
@@ -19325,7 +19326,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>362</v>
       </c>
@@ -19351,7 +19352,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>362</v>
       </c>
@@ -19377,7 +19378,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>394</v>
       </c>
@@ -19403,7 +19404,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>394</v>
       </c>
@@ -19429,7 +19430,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>394</v>
       </c>
@@ -19455,7 +19456,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>394</v>
       </c>
@@ -19481,7 +19482,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>362</v>
       </c>
@@ -19510,7 +19511,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>362</v>
       </c>
@@ -19539,7 +19540,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>362</v>
       </c>
@@ -19565,7 +19566,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>362</v>
       </c>
@@ -19591,7 +19592,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>362</v>
       </c>
@@ -19617,7 +19618,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>362</v>
       </c>
@@ -19643,7 +19644,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>362</v>
       </c>
@@ -19669,7 +19670,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>394</v>
       </c>
@@ -19695,7 +19696,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>394</v>
       </c>
@@ -19721,7 +19722,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>394</v>
       </c>
@@ -19747,7 +19748,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>394</v>
       </c>
@@ -19773,7 +19774,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>362</v>
       </c>
@@ -19802,7 +19803,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>362</v>
       </c>
@@ -19828,7 +19829,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>362</v>
       </c>
@@ -19854,7 +19855,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>394</v>
       </c>
@@ -19880,7 +19881,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
         <v>362</v>
       </c>
@@ -19909,7 +19910,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
         <v>394</v>
       </c>
@@ -19935,7 +19936,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
         <v>362</v>
       </c>
@@ -19964,7 +19965,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
         <v>362</v>
       </c>
@@ -19990,7 +19991,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
         <v>362</v>
       </c>
@@ -20019,7 +20020,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
         <v>362</v>
       </c>
@@ -20048,7 +20049,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
         <v>362</v>
       </c>
@@ -20077,7 +20078,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
         <v>362</v>
       </c>
@@ -20103,7 +20104,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
         <v>362</v>
       </c>
@@ -20129,7 +20130,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
         <v>362</v>
       </c>
@@ -20158,7 +20159,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
         <v>362</v>
       </c>
@@ -20187,7 +20188,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
         <v>362</v>
       </c>
@@ -20216,7 +20217,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
         <v>362</v>
       </c>
@@ -20245,7 +20246,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
         <v>362</v>
       </c>
@@ -20274,7 +20275,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
         <v>362</v>
       </c>
@@ -20300,7 +20301,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
         <v>362</v>
       </c>
@@ -20326,7 +20327,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
         <v>362</v>
       </c>
@@ -20355,7 +20356,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="94" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
         <v>362</v>
       </c>
@@ -20382,7 +20383,7 @@
       </c>
       <c r="I94" s="23"/>
     </row>
-    <row r="95" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
         <v>362</v>
       </c>
@@ -20409,7 +20410,7 @@
       </c>
       <c r="I95" s="23"/>
     </row>
-    <row r="96" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
         <v>362</v>
       </c>
@@ -20436,7 +20437,7 @@
       </c>
       <c r="I96" s="23"/>
     </row>
-    <row r="97" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
         <v>362</v>
       </c>
@@ -20465,7 +20466,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="98" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
         <v>362</v>
       </c>
@@ -20491,7 +20492,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="99" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
         <v>362</v>
       </c>
@@ -20517,7 +20518,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="100" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
         <v>362</v>
       </c>
@@ -20543,7 +20544,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="101" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
         <v>362</v>
       </c>
@@ -20570,7 +20571,7 @@
       </c>
       <c r="I101" s="23"/>
     </row>
-    <row r="102" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
         <v>362</v>
       </c>
@@ -20596,7 +20597,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="103" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
         <v>362</v>
       </c>
@@ -20622,7 +20623,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="104" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
         <v>362</v>
       </c>
@@ -20649,6 +20650,13 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:I104" xr:uid="{AA6C973F-831A-4595-ADBE-42068492B51B}">
+    <filterColumn colId="5">
+      <filters>
+        <filter val="market for steel, low-alloyed"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -20656,23 +20664,23 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2630534-CC44-4ECA-A706-0F71CE5AC5B4}">
   <dimension ref="A1:M423"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="20" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.28515625" customWidth="1"/>
-    <col min="3" max="3" width="51.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="20.5703125" customWidth="1"/>
-    <col min="5" max="5" width="17.85546875" customWidth="1"/>
-    <col min="6" max="6" width="15.5703125" customWidth="1"/>
-    <col min="7" max="7" width="16.85546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="27.85546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="50.7109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="41.7109375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="34.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.26953125" customWidth="1"/>
+    <col min="3" max="3" width="51.81640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.54296875" customWidth="1"/>
+    <col min="5" max="5" width="17.81640625" customWidth="1"/>
+    <col min="6" max="6" width="15.54296875" customWidth="1"/>
+    <col min="7" max="7" width="16.81640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="27.81640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="50.7265625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="41.7265625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.1796875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="34.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" s="5" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
         <v>13</v>
       </c>
@@ -20713,7 +20721,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>26</v>
       </c>
@@ -20748,7 +20756,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>26</v>
       </c>
@@ -20783,7 +20791,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="4" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>26</v>
       </c>
@@ -20820,7 +20828,7 @@
       <c r="L4"/>
       <c r="M4"/>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>26</v>
       </c>
@@ -20855,7 +20863,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>26</v>
       </c>
@@ -20890,7 +20898,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>26</v>
       </c>
@@ -20925,7 +20933,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>26</v>
       </c>
@@ -20960,7 +20968,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>26</v>
       </c>
@@ -20995,7 +21003,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>26</v>
       </c>
@@ -21033,7 +21041,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>26</v>
       </c>
@@ -21071,7 +21079,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>26</v>
       </c>
@@ -21109,7 +21117,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>26</v>
       </c>
@@ -21144,7 +21152,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>26</v>
       </c>
@@ -21179,7 +21187,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>26</v>
       </c>
@@ -21214,7 +21222,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>26</v>
       </c>
@@ -21249,7 +21257,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>26</v>
       </c>
@@ -21284,7 +21292,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A18" s="9" t="s">
         <v>26</v>
       </c>
@@ -21321,7 +21329,7 @@
       <c r="L18" s="9"/>
       <c r="M18" s="9"/>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A19" s="9" t="s">
         <v>26</v>
       </c>
@@ -21358,7 +21366,7 @@
       <c r="L19" s="9"/>
       <c r="M19" s="9"/>
     </row>
-    <row r="20" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A20" s="9" t="s">
         <v>26</v>
       </c>
@@ -21393,7 +21401,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="21" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A21" s="9" t="s">
         <v>26</v>
       </c>
@@ -21428,7 +21436,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="22" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A22" s="9" t="s">
         <v>26</v>
       </c>
@@ -21463,7 +21471,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="23" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>26</v>
       </c>
@@ -21500,7 +21508,7 @@
       <c r="L23"/>
       <c r="M23"/>
     </row>
-    <row r="24" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>26</v>
       </c>
@@ -21537,7 +21545,7 @@
       <c r="L24"/>
       <c r="M24"/>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>26</v>
       </c>
@@ -21572,7 +21580,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>26</v>
       </c>
@@ -21607,7 +21615,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>26</v>
       </c>
@@ -21642,7 +21650,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>26</v>
       </c>
@@ -21677,7 +21685,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>26</v>
       </c>
@@ -21712,7 +21720,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>26</v>
       </c>
@@ -21747,7 +21755,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>26</v>
       </c>
@@ -21782,7 +21790,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A32" s="9" t="s">
         <v>26</v>
       </c>
@@ -21819,7 +21827,7 @@
       <c r="L32" s="9"/>
       <c r="M32" s="9"/>
     </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A33" s="9" t="s">
         <v>26</v>
       </c>
@@ -21856,7 +21864,7 @@
       <c r="L33" s="9"/>
       <c r="M33" s="9"/>
     </row>
-    <row r="34" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A34" s="9" t="s">
         <v>26</v>
       </c>
@@ -21891,7 +21899,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="35" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A35" s="9" t="s">
         <v>26</v>
       </c>
@@ -21926,7 +21934,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="36" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A36" s="9" t="s">
         <v>26</v>
       </c>
@@ -21961,7 +21969,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="37" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A37" s="9" t="s">
         <v>26</v>
       </c>
@@ -21996,7 +22004,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="38" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A38" s="9" t="s">
         <v>26</v>
       </c>
@@ -22031,7 +22039,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="39" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A39" s="9" t="s">
         <v>26</v>
       </c>
@@ -22066,7 +22074,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="40" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A40" s="9" t="s">
         <v>26</v>
       </c>
@@ -22101,7 +22109,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="41" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>26</v>
       </c>
@@ -22138,7 +22146,7 @@
       <c r="L41"/>
       <c r="M41"/>
     </row>
-    <row r="42" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>26</v>
       </c>
@@ -22175,7 +22183,7 @@
       <c r="L42"/>
       <c r="M42"/>
     </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>26</v>
       </c>
@@ -22210,7 +22218,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>26</v>
       </c>
@@ -22245,7 +22253,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="45" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>26</v>
       </c>
@@ -22280,7 +22288,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="46" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>26</v>
       </c>
@@ -22315,7 +22323,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="47" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>26</v>
       </c>
@@ -22350,7 +22358,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="48" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>26</v>
       </c>
@@ -22385,7 +22393,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>26</v>
       </c>
@@ -22420,7 +22428,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>26</v>
       </c>
@@ -22455,7 +22463,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>26</v>
       </c>
@@ -22488,7 +22496,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>26</v>
       </c>
@@ -22521,7 +22529,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>26</v>
       </c>
@@ -22554,7 +22562,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>26</v>
       </c>
@@ -22587,7 +22595,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>26</v>
       </c>
@@ -22620,7 +22628,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>26</v>
       </c>
@@ -22655,7 +22663,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>26</v>
       </c>
@@ -22690,7 +22698,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>26</v>
       </c>
@@ -22725,7 +22733,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>26</v>
       </c>
@@ -22760,7 +22768,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>26</v>
       </c>
@@ -22795,7 +22803,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>26</v>
       </c>
@@ -22830,7 +22838,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>26</v>
       </c>
@@ -22865,7 +22873,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>26</v>
       </c>
@@ -22900,7 +22908,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>26</v>
       </c>
@@ -22935,7 +22943,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>26</v>
       </c>
@@ -22970,7 +22978,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>26</v>
       </c>
@@ -23005,7 +23013,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="67" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>26</v>
       </c>
@@ -23040,7 +23048,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>26</v>
       </c>
@@ -23075,7 +23083,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="69" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>26</v>
       </c>
@@ -23110,7 +23118,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="70" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>26</v>
       </c>
@@ -23145,7 +23153,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>26</v>
       </c>
@@ -23180,7 +23188,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>26</v>
       </c>
@@ -23215,7 +23223,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="73" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>26</v>
       </c>
@@ -23250,7 +23258,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="74" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>26</v>
       </c>
@@ -23285,7 +23293,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="75" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>26</v>
       </c>
@@ -23320,7 +23328,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="76" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>26</v>
       </c>
@@ -23355,7 +23363,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="77" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
         <v>26</v>
       </c>
@@ -23390,7 +23398,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="78" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
         <v>26</v>
       </c>
@@ -23425,7 +23433,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="79" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
         <v>26</v>
       </c>
@@ -23460,7 +23468,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="80" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
         <v>26</v>
       </c>
@@ -23495,7 +23503,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="81" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
         <v>26</v>
       </c>
@@ -23532,7 +23540,7 @@
       <c r="L81"/>
       <c r="M81"/>
     </row>
-    <row r="82" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
         <v>26</v>
       </c>
@@ -23569,7 +23577,7 @@
       <c r="L82"/>
       <c r="M82"/>
     </row>
-    <row r="83" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
         <v>26</v>
       </c>
@@ -23606,7 +23614,7 @@
       <c r="L83"/>
       <c r="M83"/>
     </row>
-    <row r="84" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A84" s="9" t="s">
         <v>26</v>
       </c>
@@ -23641,7 +23649,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="85" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A85" s="9" t="s">
         <v>26</v>
       </c>
@@ -23676,7 +23684,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="86" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A86" s="9" t="s">
         <v>26</v>
       </c>
@@ -23711,7 +23719,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="87" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A87" s="9" t="s">
         <v>26</v>
       </c>
@@ -23746,7 +23754,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="88" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A88" s="9" t="s">
         <v>26</v>
       </c>
@@ -23781,7 +23789,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="89" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A89" s="9" t="s">
         <v>26</v>
       </c>
@@ -23818,7 +23826,7 @@
       <c r="L89" s="9"/>
       <c r="M89" s="9"/>
     </row>
-    <row r="90" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A90" s="9" t="s">
         <v>26</v>
       </c>
@@ -23855,7 +23863,7 @@
       <c r="L90" s="9"/>
       <c r="M90" s="9"/>
     </row>
-    <row r="91" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A91" s="9" t="s">
         <v>26</v>
       </c>
@@ -23892,7 +23900,7 @@
       <c r="L91" s="9"/>
       <c r="M91" s="9"/>
     </row>
-    <row r="92" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
         <v>26</v>
       </c>
@@ -23927,7 +23935,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="93" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
         <v>26</v>
       </c>
@@ -23962,7 +23970,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="94" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
         <v>26</v>
       </c>
@@ -23997,7 +24005,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="95" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
         <v>26</v>
       </c>
@@ -24032,7 +24040,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="96" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
         <v>26</v>
       </c>
@@ -24067,7 +24075,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="97" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
         <v>26</v>
       </c>
@@ -24099,7 +24107,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="98" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
         <v>26</v>
       </c>
@@ -24131,7 +24139,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="99" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
         <v>26</v>
       </c>
@@ -24166,7 +24174,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="100" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
         <v>26</v>
       </c>
@@ -24195,7 +24203,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="101" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
         <v>26</v>
       </c>
@@ -24230,7 +24238,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="102" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
         <v>26</v>
       </c>
@@ -24265,7 +24273,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="103" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
         <v>26</v>
       </c>
@@ -24300,7 +24308,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="104" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
         <v>26</v>
       </c>
@@ -24335,7 +24343,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="105" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
         <v>26</v>
       </c>
@@ -24372,7 +24380,7 @@
       <c r="L105"/>
       <c r="M105"/>
     </row>
-    <row r="106" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
         <v>26</v>
       </c>
@@ -24409,7 +24417,7 @@
       <c r="L106"/>
       <c r="M106"/>
     </row>
-    <row r="107" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
         <v>26</v>
       </c>
@@ -24446,7 +24454,7 @@
       <c r="L107"/>
       <c r="M107"/>
     </row>
-    <row r="108" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
         <v>26</v>
       </c>
@@ -24483,7 +24491,7 @@
       <c r="L108"/>
       <c r="M108"/>
     </row>
-    <row r="109" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
         <v>26</v>
       </c>
@@ -24520,7 +24528,7 @@
       <c r="L109"/>
       <c r="M109"/>
     </row>
-    <row r="110" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
         <v>26</v>
       </c>
@@ -24557,7 +24565,7 @@
       <c r="L110"/>
       <c r="M110"/>
     </row>
-    <row r="111" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
         <v>26</v>
       </c>
@@ -24592,7 +24600,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="112" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
         <v>26</v>
       </c>
@@ -24627,7 +24635,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="113" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
         <v>26</v>
       </c>
@@ -24662,7 +24670,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="114" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
         <v>26</v>
       </c>
@@ -24697,7 +24705,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="115" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
         <v>26</v>
       </c>
@@ -24732,7 +24740,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="116" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A116" s="9" t="s">
         <v>26</v>
       </c>
@@ -24769,7 +24777,7 @@
       <c r="L116" s="9"/>
       <c r="M116" s="9"/>
     </row>
-    <row r="117" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A117" s="9" t="s">
         <v>26</v>
       </c>
@@ -24806,7 +24814,7 @@
       <c r="L117" s="9"/>
       <c r="M117" s="9"/>
     </row>
-    <row r="118" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A118" s="9" t="s">
         <v>26</v>
       </c>
@@ -24843,7 +24851,7 @@
       <c r="L118" s="9"/>
       <c r="M118" s="9"/>
     </row>
-    <row r="119" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A119" s="9" t="s">
         <v>26</v>
       </c>
@@ -24880,7 +24888,7 @@
       <c r="L119" s="9"/>
       <c r="M119" s="9"/>
     </row>
-    <row r="120" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A120" s="9" t="s">
         <v>26</v>
       </c>
@@ -24917,7 +24925,7 @@
       <c r="L120" s="9"/>
       <c r="M120" s="9"/>
     </row>
-    <row r="121" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A121" s="9" t="s">
         <v>26</v>
       </c>
@@ -24952,7 +24960,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="122" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A122" s="11" t="s">
         <v>26</v>
       </c>
@@ -24989,7 +24997,7 @@
       <c r="L122" s="11"/>
       <c r="M122" s="11"/>
     </row>
-    <row r="123" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A123" s="11" t="s">
         <v>26</v>
       </c>
@@ -25026,7 +25034,7 @@
       <c r="L123" s="11"/>
       <c r="M123" s="11"/>
     </row>
-    <row r="124" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A124" s="11" t="s">
         <v>26</v>
       </c>
@@ -25063,7 +25071,7 @@
       <c r="L124" s="11"/>
       <c r="M124" s="11"/>
     </row>
-    <row r="125" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A125" s="11" t="s">
         <v>26</v>
       </c>
@@ -25100,7 +25108,7 @@
       <c r="L125" s="11"/>
       <c r="M125" s="11"/>
     </row>
-    <row r="126" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A126" s="11" t="s">
         <v>26</v>
       </c>
@@ -25137,7 +25145,7 @@
       <c r="L126" s="11"/>
       <c r="M126" s="11"/>
     </row>
-    <row r="127" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
         <v>26</v>
       </c>
@@ -25174,7 +25182,7 @@
       <c r="L127"/>
       <c r="M127"/>
     </row>
-    <row r="128" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
         <v>26</v>
       </c>
@@ -25211,7 +25219,7 @@
       <c r="L128"/>
       <c r="M128"/>
     </row>
-    <row r="129" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
         <v>26</v>
       </c>
@@ -25248,7 +25256,7 @@
       <c r="L129"/>
       <c r="M129"/>
     </row>
-    <row r="130" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
         <v>26</v>
       </c>
@@ -25285,7 +25293,7 @@
       <c r="L130"/>
       <c r="M130"/>
     </row>
-    <row r="131" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
         <v>26</v>
       </c>
@@ -25322,7 +25330,7 @@
       <c r="L131"/>
       <c r="M131"/>
     </row>
-    <row r="132" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A132" s="9" t="s">
         <v>26</v>
       </c>
@@ -25357,7 +25365,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="133" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A133" s="9" t="s">
         <v>26</v>
       </c>
@@ -25392,7 +25400,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="134" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A134" s="9" t="s">
         <v>26</v>
       </c>
@@ -25427,7 +25435,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="135" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A135" s="9" t="s">
         <v>26</v>
       </c>
@@ -25464,7 +25472,7 @@
       <c r="L135" s="9"/>
       <c r="M135" s="9"/>
     </row>
-    <row r="136" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A136" s="9" t="s">
         <v>26</v>
       </c>
@@ -25501,7 +25509,7 @@
       <c r="L136" s="9"/>
       <c r="M136" s="9"/>
     </row>
-    <row r="137" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A137" s="9" t="s">
         <v>26</v>
       </c>
@@ -25538,7 +25546,7 @@
       <c r="L137" s="9"/>
       <c r="M137" s="9"/>
     </row>
-    <row r="138" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A138" s="9" t="s">
         <v>26</v>
       </c>
@@ -25575,7 +25583,7 @@
       <c r="L138" s="9"/>
       <c r="M138" s="9"/>
     </row>
-    <row r="139" spans="1:13" s="11" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:13" s="11" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A139" s="9" t="s">
         <v>26</v>
       </c>
@@ -25612,7 +25620,7 @@
       <c r="L139" s="9"/>
       <c r="M139" s="9"/>
     </row>
-    <row r="140" spans="1:13" s="11" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:13" s="11" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A140" s="9" t="s">
         <v>26</v>
       </c>
@@ -25649,7 +25657,7 @@
       <c r="L140" s="9"/>
       <c r="M140" s="9"/>
     </row>
-    <row r="141" spans="1:13" s="11" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:13" s="11" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A141" s="9" t="s">
         <v>26</v>
       </c>
@@ -25686,7 +25694,7 @@
       <c r="L141" s="9"/>
       <c r="M141" s="9"/>
     </row>
-    <row r="142" spans="1:13" s="11" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:13" s="11" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A142" s="9" t="s">
         <v>26</v>
       </c>
@@ -25723,7 +25731,7 @@
       <c r="L142" s="9"/>
       <c r="M142" s="9"/>
     </row>
-    <row r="143" spans="1:13" s="11" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:13" s="11" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A143" s="9" t="s">
         <v>26</v>
       </c>
@@ -25760,7 +25768,7 @@
       <c r="L143" s="9"/>
       <c r="M143" s="9"/>
     </row>
-    <row r="144" spans="1:13" s="11" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:13" s="11" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A144" s="9" t="s">
         <v>26</v>
       </c>
@@ -25797,7 +25805,7 @@
       <c r="L144" s="9"/>
       <c r="M144" s="9"/>
     </row>
-    <row r="145" spans="1:13" s="11" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:13" s="11" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A145" s="9" t="s">
         <v>26</v>
       </c>
@@ -25834,7 +25842,7 @@
       <c r="L145" s="9"/>
       <c r="M145" s="9"/>
     </row>
-    <row r="146" spans="1:13" s="11" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:13" s="11" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A146" t="s">
         <v>26</v>
       </c>
@@ -25871,7 +25879,7 @@
       <c r="L146"/>
       <c r="M146"/>
     </row>
-    <row r="147" spans="1:13" s="11" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:13" s="11" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A147" t="s">
         <v>26</v>
       </c>
@@ -25908,7 +25916,7 @@
       <c r="L147"/>
       <c r="M147"/>
     </row>
-    <row r="148" spans="1:13" s="11" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:13" s="11" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A148" t="s">
         <v>26</v>
       </c>
@@ -25945,7 +25953,7 @@
       <c r="L148"/>
       <c r="M148"/>
     </row>
-    <row r="149" spans="1:13" s="11" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:13" s="11" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A149" t="s">
         <v>26</v>
       </c>
@@ -25982,7 +25990,7 @@
       <c r="L149"/>
       <c r="M149"/>
     </row>
-    <row r="150" spans="1:13" s="11" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:13" s="11" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A150" t="s">
         <v>26</v>
       </c>
@@ -26019,7 +26027,7 @@
       <c r="L150"/>
       <c r="M150"/>
     </row>
-    <row r="151" spans="1:13" s="11" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:13" s="11" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A151" s="11" t="s">
         <v>26</v>
       </c>
@@ -26054,7 +26062,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="152" spans="1:13" s="11" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:13" s="11" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A152" s="11" t="s">
         <v>26</v>
       </c>
@@ -26089,7 +26097,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="153" spans="1:13" s="11" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:13" s="11" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A153" s="11" t="s">
         <v>26</v>
       </c>
@@ -26124,7 +26132,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="154" spans="1:13" s="11" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:13" s="11" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A154" t="s">
         <v>26</v>
       </c>
@@ -26161,7 +26169,7 @@
       <c r="L154"/>
       <c r="M154"/>
     </row>
-    <row r="155" spans="1:13" s="11" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:13" s="11" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A155" t="s">
         <v>26</v>
       </c>
@@ -26198,7 +26206,7 @@
       <c r="L155"/>
       <c r="M155"/>
     </row>
-    <row r="156" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A156" s="13" t="s">
         <v>26</v>
       </c>
@@ -26237,7 +26245,7 @@
       </c>
       <c r="M156" s="13"/>
     </row>
-    <row r="157" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A157" s="13" t="s">
         <v>26</v>
       </c>
@@ -26276,7 +26284,7 @@
       </c>
       <c r="M157" s="13"/>
     </row>
-    <row r="158" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A158" t="s">
         <v>26</v>
       </c>
@@ -26308,7 +26316,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="159" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A159" t="s">
         <v>26</v>
       </c>
@@ -26340,7 +26348,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="160" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A160" t="s">
         <v>26</v>
       </c>
@@ -26375,7 +26383,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="161" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A161" t="s">
         <v>26</v>
       </c>
@@ -26410,7 +26418,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="162" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A162" t="s">
         <v>26</v>
       </c>
@@ -26445,7 +26453,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="163" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A163" t="s">
         <v>26</v>
       </c>
@@ -26480,7 +26488,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="164" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A164" t="s">
         <v>26</v>
       </c>
@@ -26515,7 +26523,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="165" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A165" t="s">
         <v>26</v>
       </c>
@@ -26550,7 +26558,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="166" spans="1:13" s="13" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:13" s="13" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A166" t="s">
         <v>26</v>
       </c>
@@ -26587,7 +26595,7 @@
       <c r="L166"/>
       <c r="M166"/>
     </row>
-    <row r="167" spans="1:13" s="13" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:13" s="13" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A167" t="s">
         <v>26</v>
       </c>
@@ -26624,7 +26632,7 @@
       <c r="L167"/>
       <c r="M167"/>
     </row>
-    <row r="168" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A168" t="s">
         <v>26</v>
       </c>
@@ -26659,7 +26667,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="169" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A169" t="s">
         <v>26</v>
       </c>
@@ -26694,7 +26702,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="170" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A170" t="s">
         <v>26</v>
       </c>
@@ -26729,7 +26737,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="171" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A171" t="s">
         <v>26</v>
       </c>
@@ -26764,7 +26772,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="172" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A172" t="s">
         <v>26</v>
       </c>
@@ -26799,7 +26807,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="173" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A173" t="s">
         <v>26</v>
       </c>
@@ -26834,7 +26842,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="174" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A174" t="s">
         <v>26</v>
       </c>
@@ -26869,7 +26877,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="175" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A175" t="s">
         <v>26</v>
       </c>
@@ -26904,7 +26912,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="176" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A176" t="s">
         <v>26</v>
       </c>
@@ -26939,7 +26947,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="177" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A177" t="s">
         <v>26</v>
       </c>
@@ -26974,7 +26982,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="178" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A178" t="s">
         <v>26</v>
       </c>
@@ -27009,7 +27017,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="179" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A179" t="s">
         <v>26</v>
       </c>
@@ -27044,7 +27052,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="180" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A180" t="s">
         <v>26</v>
       </c>
@@ -27079,7 +27087,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="181" spans="1:13" s="11" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:13" s="11" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A181" t="s">
         <v>26</v>
       </c>
@@ -27116,7 +27124,7 @@
       <c r="L181"/>
       <c r="M181"/>
     </row>
-    <row r="182" spans="1:13" s="11" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:13" s="11" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A182" t="s">
         <v>26</v>
       </c>
@@ -27153,7 +27161,7 @@
       <c r="L182"/>
       <c r="M182"/>
     </row>
-    <row r="183" spans="1:13" s="11" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:13" s="11" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A183" t="s">
         <v>26</v>
       </c>
@@ -27190,7 +27198,7 @@
       <c r="L183"/>
       <c r="M183"/>
     </row>
-    <row r="184" spans="1:13" s="11" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:13" s="11" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A184" t="s">
         <v>26</v>
       </c>
@@ -27227,7 +27235,7 @@
       <c r="L184"/>
       <c r="M184"/>
     </row>
-    <row r="185" spans="1:13" s="11" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:13" s="11" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A185" t="s">
         <v>26</v>
       </c>
@@ -27264,7 +27272,7 @@
       <c r="L185"/>
       <c r="M185"/>
     </row>
-    <row r="186" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A186" t="s">
         <v>26</v>
       </c>
@@ -27299,7 +27307,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="187" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A187" t="s">
         <v>26</v>
       </c>
@@ -27334,7 +27342,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="188" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A188" t="s">
         <v>26</v>
       </c>
@@ -27369,7 +27377,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="189" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A189" t="s">
         <v>26</v>
       </c>
@@ -27404,7 +27412,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="190" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A190" t="s">
         <v>26</v>
       </c>
@@ -27439,7 +27447,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="191" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A191" t="s">
         <v>26</v>
       </c>
@@ -27474,7 +27482,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="192" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A192" t="s">
         <v>26</v>
       </c>
@@ -27509,7 +27517,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="193" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A193" t="s">
         <v>26</v>
       </c>
@@ -27544,7 +27552,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="194" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A194" t="s">
         <v>26</v>
       </c>
@@ -27579,7 +27587,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="195" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A195" t="s">
         <v>26</v>
       </c>
@@ -27614,7 +27622,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="196" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A196" t="s">
         <v>26</v>
       </c>
@@ -27649,7 +27657,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="197" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A197" t="s">
         <v>26</v>
       </c>
@@ -27684,7 +27692,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="198" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A198" t="s">
         <v>26</v>
       </c>
@@ -27719,7 +27727,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="199" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A199" t="s">
         <v>26</v>
       </c>
@@ -27754,7 +27762,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="200" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A200" t="s">
         <v>26</v>
       </c>
@@ -27789,7 +27797,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="201" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A201" t="s">
         <v>26</v>
       </c>
@@ -27824,7 +27832,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="202" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A202" t="s">
         <v>26</v>
       </c>
@@ -27859,7 +27867,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="203" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A203" t="s">
         <v>26</v>
       </c>
@@ -27894,7 +27902,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="204" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A204" t="s">
         <v>26</v>
       </c>
@@ -27929,7 +27937,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="205" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A205" t="s">
         <v>26</v>
       </c>
@@ -27964,7 +27972,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="206" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A206" t="s">
         <v>26</v>
       </c>
@@ -27999,7 +28007,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="207" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A207" t="s">
         <v>26</v>
       </c>
@@ -28034,7 +28042,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="208" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A208" t="s">
         <v>26</v>
       </c>
@@ -28069,7 +28077,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="209" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A209" t="s">
         <v>26</v>
       </c>
@@ -28104,7 +28112,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="210" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A210" t="s">
         <v>26</v>
       </c>
@@ -28139,7 +28147,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="211" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A211" t="s">
         <v>26</v>
       </c>
@@ -28174,7 +28182,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="212" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A212" t="s">
         <v>26</v>
       </c>
@@ -28209,7 +28217,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="213" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A213" s="9" t="s">
         <v>26</v>
       </c>
@@ -28246,7 +28254,7 @@
       <c r="L213" s="9"/>
       <c r="M213" s="9"/>
     </row>
-    <row r="214" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A214" s="9" t="s">
         <v>26</v>
       </c>
@@ -28283,7 +28291,7 @@
       <c r="L214" s="9"/>
       <c r="M214" s="9"/>
     </row>
-    <row r="215" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A215" s="9" t="s">
         <v>26</v>
       </c>
@@ -28318,7 +28326,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="216" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A216" s="9" t="s">
         <v>26</v>
       </c>
@@ -28353,7 +28361,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="217" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A217" s="9" t="s">
         <v>26</v>
       </c>
@@ -28388,7 +28396,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="218" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A218" s="9" t="s">
         <v>26</v>
       </c>
@@ -28423,7 +28431,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="219" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A219" s="9" t="s">
         <v>26</v>
       </c>
@@ -28458,7 +28466,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="220" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A220" s="9" t="s">
         <v>26</v>
       </c>
@@ -28493,7 +28501,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="221" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A221" s="9" t="s">
         <v>26</v>
       </c>
@@ -28528,7 +28536,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="222" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A222" t="s">
         <v>26</v>
       </c>
@@ -28565,7 +28573,7 @@
       <c r="L222"/>
       <c r="M222"/>
     </row>
-    <row r="223" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A223" t="s">
         <v>26</v>
       </c>
@@ -28602,7 +28610,7 @@
       <c r="L223"/>
       <c r="M223"/>
     </row>
-    <row r="224" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A224" t="s">
         <v>26</v>
       </c>
@@ -28637,7 +28645,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="225" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A225" t="s">
         <v>26</v>
       </c>
@@ -28672,7 +28680,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="226" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A226" t="s">
         <v>26</v>
       </c>
@@ -28707,7 +28715,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="227" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A227" t="s">
         <v>26</v>
       </c>
@@ -28742,7 +28750,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="228" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A228" t="s">
         <v>26</v>
       </c>
@@ -28777,7 +28785,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="229" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A229" t="s">
         <v>26</v>
       </c>
@@ -28812,7 +28820,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="230" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A230" s="11" t="s">
         <v>26</v>
       </c>
@@ -28851,7 +28859,7 @@
       </c>
       <c r="M230" s="11"/>
     </row>
-    <row r="231" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A231" s="11" t="s">
         <v>26</v>
       </c>
@@ -28890,7 +28898,7 @@
       </c>
       <c r="M231" s="11"/>
     </row>
-    <row r="232" spans="1:13" s="11" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:13" s="11" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A232" s="11" t="s">
         <v>26</v>
       </c>
@@ -28928,7 +28936,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="233" spans="1:13" s="11" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:13" s="11" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A233" s="11" t="s">
         <v>26</v>
       </c>
@@ -28966,7 +28974,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="234" spans="1:13" s="11" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:13" s="11" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A234" s="11" t="s">
         <v>26</v>
       </c>
@@ -29004,7 +29012,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="235" spans="1:13" s="11" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:13" s="11" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A235" s="11" t="s">
         <v>26</v>
       </c>
@@ -29039,7 +29047,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="236" spans="1:13" s="11" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:13" s="11" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A236" s="11" t="s">
         <v>26</v>
       </c>
@@ -29074,7 +29082,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="237" spans="1:13" s="11" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:13" s="11" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A237" s="11" t="s">
         <v>26</v>
       </c>
@@ -29109,7 +29117,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="238" spans="1:13" s="11" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:13" s="11" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A238" t="s">
         <v>26</v>
       </c>
@@ -29146,7 +29154,7 @@
       <c r="L238"/>
       <c r="M238"/>
     </row>
-    <row r="239" spans="1:13" s="11" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:13" s="11" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A239" t="s">
         <v>26</v>
       </c>
@@ -29183,7 +29191,7 @@
       <c r="L239"/>
       <c r="M239"/>
     </row>
-    <row r="240" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A240" t="s">
         <v>26</v>
       </c>
@@ -29218,7 +29226,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="241" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A241" t="s">
         <v>26</v>
       </c>
@@ -29253,7 +29261,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="242" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A242" t="s">
         <v>26</v>
       </c>
@@ -29288,7 +29296,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="243" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A243" t="s">
         <v>26</v>
       </c>
@@ -29323,7 +29331,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="244" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A244" t="s">
         <v>26</v>
       </c>
@@ -29358,7 +29366,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="245" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A245" t="s">
         <v>26</v>
       </c>
@@ -29393,7 +29401,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="246" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A246" s="9" t="s">
         <v>26</v>
       </c>
@@ -29430,7 +29438,7 @@
       <c r="L246" s="9"/>
       <c r="M246" s="9"/>
     </row>
-    <row r="247" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A247" s="9" t="s">
         <v>26</v>
       </c>
@@ -29467,7 +29475,7 @@
       <c r="L247" s="9"/>
       <c r="M247" s="9"/>
     </row>
-    <row r="248" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A248" s="9" t="s">
         <v>26</v>
       </c>
@@ -29502,7 +29510,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="249" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A249" s="9" t="s">
         <v>26</v>
       </c>
@@ -29537,7 +29545,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="250" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A250" s="9" t="s">
         <v>26</v>
       </c>
@@ -29572,7 +29580,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="251" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A251" s="9" t="s">
         <v>26</v>
       </c>
@@ -29607,7 +29615,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="252" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A252" s="9" t="s">
         <v>26</v>
       </c>
@@ -29642,7 +29650,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="253" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A253" s="9" t="s">
         <v>26</v>
       </c>
@@ -29677,7 +29685,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="254" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A254" t="s">
         <v>26</v>
       </c>
@@ -29712,7 +29720,7 @@
       <c r="L254"/>
       <c r="M254"/>
     </row>
-    <row r="255" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A255" t="s">
         <v>26</v>
       </c>
@@ -29747,7 +29755,7 @@
       <c r="L255"/>
       <c r="M255"/>
     </row>
-    <row r="256" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A256" t="s">
         <v>26</v>
       </c>
@@ -29782,7 +29790,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="257" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A257" t="s">
         <v>26</v>
       </c>
@@ -29817,7 +29825,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="258" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A258" t="s">
         <v>26</v>
       </c>
@@ -29852,7 +29860,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="259" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A259" t="s">
         <v>26</v>
       </c>
@@ -29887,7 +29895,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="260" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A260" t="s">
         <v>26</v>
       </c>
@@ -29922,7 +29930,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="261" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A261" t="s">
         <v>26</v>
       </c>
@@ -29957,7 +29965,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="262" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A262" t="s">
         <v>26</v>
       </c>
@@ -29992,7 +30000,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="263" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A263" t="s">
         <v>26</v>
       </c>
@@ -30027,7 +30035,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="264" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A264" t="s">
         <v>26</v>
       </c>
@@ -30062,7 +30070,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="265" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A265" s="9" t="s">
         <v>26</v>
       </c>
@@ -30099,7 +30107,7 @@
       <c r="L265" s="9"/>
       <c r="M265" s="9"/>
     </row>
-    <row r="266" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A266" s="9" t="s">
         <v>26</v>
       </c>
@@ -30136,7 +30144,7 @@
       <c r="L266" s="9"/>
       <c r="M266" s="9"/>
     </row>
-    <row r="267" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A267" s="9" t="s">
         <v>26</v>
       </c>
@@ -30173,7 +30181,7 @@
       <c r="L267" s="9"/>
       <c r="M267" s="9"/>
     </row>
-    <row r="268" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A268" s="9" t="s">
         <v>26</v>
       </c>
@@ -30208,7 +30216,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="269" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A269" s="9" t="s">
         <v>26</v>
       </c>
@@ -30243,7 +30251,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="270" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A270" s="9" t="s">
         <v>26</v>
       </c>
@@ -30278,7 +30286,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="271" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A271" t="s">
         <v>26</v>
       </c>
@@ -30315,7 +30323,7 @@
       <c r="L271"/>
       <c r="M271"/>
     </row>
-    <row r="272" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A272" t="s">
         <v>26</v>
       </c>
@@ -30352,7 +30360,7 @@
       <c r="L272"/>
       <c r="M272"/>
     </row>
-    <row r="273" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A273" t="s">
         <v>26</v>
       </c>
@@ -30389,7 +30397,7 @@
       <c r="L273"/>
       <c r="M273"/>
     </row>
-    <row r="274" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A274" t="s">
         <v>26</v>
       </c>
@@ -30427,7 +30435,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="275" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A275" t="s">
         <v>26</v>
       </c>
@@ -30462,7 +30470,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="276" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A276" t="s">
         <v>26</v>
       </c>
@@ -30497,7 +30505,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="277" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A277" t="s">
         <v>26</v>
       </c>
@@ -30532,7 +30540,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="278" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A278" t="s">
         <v>26</v>
       </c>
@@ -30567,7 +30575,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="279" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A279" t="s">
         <v>26</v>
       </c>
@@ -30602,7 +30610,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="280" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A280" t="s">
         <v>26</v>
       </c>
@@ -30637,7 +30645,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="281" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A281" t="s">
         <v>26</v>
       </c>
@@ -30672,7 +30680,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="282" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A282" s="15" t="s">
         <v>26</v>
       </c>
@@ -30711,7 +30719,7 @@
       </c>
       <c r="M282" s="15"/>
     </row>
-    <row r="283" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A283" s="15" t="s">
         <v>26</v>
       </c>
@@ -30750,7 +30758,7 @@
       </c>
       <c r="M283" s="15"/>
     </row>
-    <row r="284" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A284" s="15" t="s">
         <v>26</v>
       </c>
@@ -30789,7 +30797,7 @@
       </c>
       <c r="M284" s="15"/>
     </row>
-    <row r="285" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A285" s="15" t="s">
         <v>26</v>
       </c>
@@ -30828,7 +30836,7 @@
       </c>
       <c r="M285" s="15"/>
     </row>
-    <row r="286" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A286" s="15" t="s">
         <v>26</v>
       </c>
@@ -30867,7 +30875,7 @@
       </c>
       <c r="M286" s="15"/>
     </row>
-    <row r="287" spans="1:13" s="17" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:13" s="17" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A287" s="15" t="s">
         <v>26</v>
       </c>
@@ -30906,7 +30914,7 @@
       </c>
       <c r="M287" s="15"/>
     </row>
-    <row r="288" spans="1:13" s="17" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:13" s="17" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A288" t="s">
         <v>26</v>
       </c>
@@ -30939,7 +30947,7 @@
       <c r="L288"/>
       <c r="M288"/>
     </row>
-    <row r="289" spans="1:13" s="17" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:13" s="17" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A289" t="s">
         <v>26</v>
       </c>
@@ -30972,7 +30980,7 @@
       <c r="L289"/>
       <c r="M289"/>
     </row>
-    <row r="290" spans="1:13" s="17" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:13" s="17" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A290" s="9" t="s">
         <v>26</v>
       </c>
@@ -31011,7 +31019,7 @@
       </c>
       <c r="M290" s="9"/>
     </row>
-    <row r="291" spans="1:13" s="17" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:13" s="17" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A291" s="11" t="s">
         <v>26</v>
       </c>
@@ -31050,7 +31058,7 @@
       </c>
       <c r="M291" s="11"/>
     </row>
-    <row r="292" spans="1:13" s="13" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:13" s="13" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A292" s="11" t="s">
         <v>26</v>
       </c>
@@ -31089,7 +31097,7 @@
       </c>
       <c r="M292" s="11"/>
     </row>
-    <row r="293" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A293" s="11" t="s">
         <v>26</v>
       </c>
@@ -31128,7 +31136,7 @@
       </c>
       <c r="M293" s="11"/>
     </row>
-    <row r="294" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A294" s="11" t="s">
         <v>26</v>
       </c>
@@ -31167,7 +31175,7 @@
       </c>
       <c r="M294" s="11"/>
     </row>
-    <row r="295" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A295" s="11" t="s">
         <v>26</v>
       </c>
@@ -31206,7 +31214,7 @@
       </c>
       <c r="M295" s="11"/>
     </row>
-    <row r="296" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A296" s="11" t="s">
         <v>26</v>
       </c>
@@ -31245,7 +31253,7 @@
       </c>
       <c r="M296" s="11"/>
     </row>
-    <row r="297" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A297" s="11" t="s">
         <v>26</v>
       </c>
@@ -31284,7 +31292,7 @@
       </c>
       <c r="M297" s="11"/>
     </row>
-    <row r="298" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A298" s="11" t="s">
         <v>26</v>
       </c>
@@ -31323,7 +31331,7 @@
       </c>
       <c r="M298" s="11"/>
     </row>
-    <row r="299" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A299" s="11" t="s">
         <v>26</v>
       </c>
@@ -31362,7 +31370,7 @@
       </c>
       <c r="M299" s="11"/>
     </row>
-    <row r="300" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A300" s="11" t="s">
         <v>26</v>
       </c>
@@ -31401,7 +31409,7 @@
       </c>
       <c r="M300" s="11"/>
     </row>
-    <row r="301" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A301" s="11" t="s">
         <v>26</v>
       </c>
@@ -31440,7 +31448,7 @@
       </c>
       <c r="M301" s="11"/>
     </row>
-    <row r="302" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A302" s="11" t="s">
         <v>26</v>
       </c>
@@ -31479,7 +31487,7 @@
       </c>
       <c r="M302" s="11"/>
     </row>
-    <row r="303" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A303" s="11" t="s">
         <v>26</v>
       </c>
@@ -31518,7 +31526,7 @@
       </c>
       <c r="M303" s="11"/>
     </row>
-    <row r="304" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A304" s="11" t="s">
         <v>26</v>
       </c>
@@ -31557,7 +31565,7 @@
       </c>
       <c r="M304" s="11"/>
     </row>
-    <row r="305" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A305" t="s">
         <v>26</v>
       </c>
@@ -31595,7 +31603,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="306" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A306" s="17" t="s">
         <v>26</v>
       </c>
@@ -31634,7 +31642,7 @@
       </c>
       <c r="M306" s="17"/>
     </row>
-    <row r="307" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A307" s="17" t="s">
         <v>26</v>
       </c>
@@ -31673,7 +31681,7 @@
       </c>
       <c r="M307" s="17"/>
     </row>
-    <row r="308" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A308" s="17" t="s">
         <v>26</v>
       </c>
@@ -31712,7 +31720,7 @@
       </c>
       <c r="M308" s="17"/>
     </row>
-    <row r="309" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A309" s="17" t="s">
         <v>26</v>
       </c>
@@ -31751,7 +31759,7 @@
       </c>
       <c r="M309" s="17"/>
     </row>
-    <row r="310" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A310" s="17" t="s">
         <v>26</v>
       </c>
@@ -31790,7 +31798,7 @@
       </c>
       <c r="M310" s="17"/>
     </row>
-    <row r="311" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A311" t="s">
         <v>26</v>
       </c>
@@ -31828,7 +31836,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="312" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A312" t="s">
         <v>26</v>
       </c>
@@ -31866,7 +31874,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="313" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A313" t="s">
         <v>26</v>
       </c>
@@ -31904,7 +31912,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="314" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A314" t="s">
         <v>26</v>
       </c>
@@ -31942,7 +31950,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="315" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A315" t="s">
         <v>26</v>
       </c>
@@ -31980,7 +31988,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="316" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A316" t="s">
         <v>26</v>
       </c>
@@ -32018,7 +32026,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="317" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A317" t="s">
         <v>26</v>
       </c>
@@ -32056,7 +32064,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="318" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A318" t="s">
         <v>26</v>
       </c>
@@ -32091,7 +32099,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="319" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A319" t="s">
         <v>26</v>
       </c>
@@ -32126,7 +32134,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="320" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A320" t="s">
         <v>26</v>
       </c>
@@ -32161,7 +32169,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="321" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A321" t="s">
         <v>26</v>
       </c>
@@ -32196,7 +32204,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="322" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A322" t="s">
         <v>26</v>
       </c>
@@ -32231,7 +32239,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="323" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A323" t="s">
         <v>26</v>
       </c>
@@ -32266,7 +32274,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="324" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A324" t="s">
         <v>26</v>
       </c>
@@ -32301,7 +32309,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="325" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A325" t="s">
         <v>26</v>
       </c>
@@ -32336,7 +32344,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="326" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A326" t="s">
         <v>26</v>
       </c>
@@ -32371,7 +32379,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="327" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A327" t="s">
         <v>26</v>
       </c>
@@ -32406,7 +32414,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="328" spans="1:13" s="13" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:13" s="13" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A328" t="s">
         <v>26</v>
       </c>
@@ -32443,7 +32451,7 @@
       <c r="L328"/>
       <c r="M328"/>
     </row>
-    <row r="329" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A329" t="s">
         <v>26</v>
       </c>
@@ -32478,7 +32486,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="330" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A330" t="s">
         <v>26</v>
       </c>
@@ -32513,7 +32521,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="331" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A331" t="s">
         <v>26</v>
       </c>
@@ -32548,7 +32556,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="332" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A332" t="s">
         <v>26</v>
       </c>
@@ -32583,7 +32591,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="333" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A333" t="s">
         <v>26</v>
       </c>
@@ -32618,7 +32626,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="334" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A334" t="s">
         <v>26</v>
       </c>
@@ -32653,7 +32661,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="335" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A335" t="s">
         <v>26</v>
       </c>
@@ -32688,7 +32696,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="336" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A336" t="s">
         <v>26</v>
       </c>
@@ -32723,7 +32731,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="337" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A337" t="s">
         <v>26</v>
       </c>
@@ -32758,7 +32766,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="338" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A338" t="s">
         <v>26</v>
       </c>
@@ -32795,7 +32803,7 @@
       <c r="L338"/>
       <c r="M338"/>
     </row>
-    <row r="339" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A339" t="s">
         <v>26</v>
       </c>
@@ -32834,7 +32842,7 @@
       </c>
       <c r="M339"/>
     </row>
-    <row r="340" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A340" t="s">
         <v>26</v>
       </c>
@@ -32873,7 +32881,7 @@
       </c>
       <c r="M340"/>
     </row>
-    <row r="341" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A341" t="s">
         <v>26</v>
       </c>
@@ -32912,7 +32920,7 @@
       </c>
       <c r="M341"/>
     </row>
-    <row r="342" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A342" t="s">
         <v>26</v>
       </c>
@@ -32951,7 +32959,7 @@
       </c>
       <c r="M342"/>
     </row>
-    <row r="343" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A343" t="s">
         <v>26</v>
       </c>
@@ -32988,7 +32996,7 @@
       <c r="L343"/>
       <c r="M343"/>
     </row>
-    <row r="344" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A344" t="s">
         <v>26</v>
       </c>
@@ -33025,7 +33033,7 @@
       <c r="L344"/>
       <c r="M344"/>
     </row>
-    <row r="345" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A345" t="s">
         <v>26</v>
       </c>
@@ -33062,7 +33070,7 @@
       <c r="L345"/>
       <c r="M345"/>
     </row>
-    <row r="346" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A346" t="s">
         <v>26</v>
       </c>
@@ -33099,7 +33107,7 @@
       <c r="L346"/>
       <c r="M346"/>
     </row>
-    <row r="347" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A347" t="s">
         <v>26</v>
       </c>
@@ -33136,7 +33144,7 @@
       <c r="L347"/>
       <c r="M347"/>
     </row>
-    <row r="348" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A348" t="s">
         <v>26</v>
       </c>
@@ -33173,7 +33181,7 @@
       <c r="L348"/>
       <c r="M348"/>
     </row>
-    <row r="349" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A349" t="s">
         <v>26</v>
       </c>
@@ -33210,7 +33218,7 @@
       <c r="L349"/>
       <c r="M349"/>
     </row>
-    <row r="350" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A350" t="s">
         <v>26</v>
       </c>
@@ -33247,7 +33255,7 @@
       <c r="L350"/>
       <c r="M350"/>
     </row>
-    <row r="351" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A351" t="s">
         <v>26</v>
       </c>
@@ -33282,7 +33290,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="352" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A352" t="s">
         <v>26</v>
       </c>
@@ -33317,7 +33325,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="353" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A353" t="s">
         <v>26</v>
       </c>
@@ -33352,7 +33360,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="354" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A354" t="s">
         <v>26</v>
       </c>
@@ -33387,7 +33395,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="355" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A355" t="s">
         <v>26</v>
       </c>
@@ -33422,7 +33430,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="356" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A356" t="s">
         <v>26</v>
       </c>
@@ -33457,7 +33465,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="357" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A357" t="s">
         <v>26</v>
       </c>
@@ -33492,7 +33500,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="358" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A358" t="s">
         <v>26</v>
       </c>
@@ -33527,7 +33535,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="359" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A359" s="9" t="s">
         <v>26</v>
       </c>
@@ -33564,7 +33572,7 @@
       <c r="L359" s="9"/>
       <c r="M359" s="9"/>
     </row>
-    <row r="360" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A360" s="9" t="s">
         <v>26</v>
       </c>
@@ -33601,7 +33609,7 @@
       <c r="L360" s="9"/>
       <c r="M360" s="9"/>
     </row>
-    <row r="361" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A361" s="9" t="s">
         <v>26</v>
       </c>
@@ -33638,7 +33646,7 @@
       <c r="L361" s="9"/>
       <c r="M361" s="9"/>
     </row>
-    <row r="362" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A362" s="9" t="s">
         <v>26</v>
       </c>
@@ -33675,7 +33683,7 @@
       <c r="L362" s="9"/>
       <c r="M362" s="9"/>
     </row>
-    <row r="363" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A363" s="9" t="s">
         <v>26</v>
       </c>
@@ -33712,7 +33720,7 @@
       <c r="L363" s="9"/>
       <c r="M363" s="9"/>
     </row>
-    <row r="364" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A364" s="9" t="s">
         <v>26</v>
       </c>
@@ -33749,7 +33757,7 @@
       <c r="L364" s="9"/>
       <c r="M364" s="9"/>
     </row>
-    <row r="365" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A365" s="9" t="s">
         <v>26</v>
       </c>
@@ -33786,7 +33794,7 @@
       <c r="L365" s="9"/>
       <c r="M365" s="9"/>
     </row>
-    <row r="366" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A366" s="9" t="s">
         <v>26</v>
       </c>
@@ -33823,7 +33831,7 @@
       <c r="L366" s="9"/>
       <c r="M366" s="9"/>
     </row>
-    <row r="367" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A367" s="9" t="s">
         <v>26</v>
       </c>
@@ -33860,7 +33868,7 @@
       <c r="L367" s="9"/>
       <c r="M367" s="9"/>
     </row>
-    <row r="368" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A368" s="9" t="s">
         <v>26</v>
       </c>
@@ -33895,7 +33903,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="369" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A369" s="9" t="s">
         <v>26</v>
       </c>
@@ -33930,7 +33938,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="370" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A370" s="9" t="s">
         <v>26</v>
       </c>
@@ -33965,7 +33973,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="371" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A371" s="9" t="s">
         <v>26</v>
       </c>
@@ -34000,7 +34008,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="372" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A372" t="s">
         <v>26</v>
       </c>
@@ -34037,7 +34045,7 @@
       <c r="L372"/>
       <c r="M372"/>
     </row>
-    <row r="373" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A373" t="s">
         <v>26</v>
       </c>
@@ -34074,7 +34082,7 @@
       <c r="L373"/>
       <c r="M373"/>
     </row>
-    <row r="374" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A374" t="s">
         <v>26</v>
       </c>
@@ -34109,7 +34117,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="375" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A375" t="s">
         <v>26</v>
       </c>
@@ -34144,7 +34152,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="376" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A376" t="s">
         <v>26</v>
       </c>
@@ -34182,7 +34190,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="377" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A377" t="s">
         <v>26</v>
       </c>
@@ -34220,7 +34228,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="378" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A378" t="s">
         <v>26</v>
       </c>
@@ -34258,7 +34266,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="379" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A379" t="s">
         <v>26</v>
       </c>
@@ -34296,7 +34304,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="380" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A380" t="s">
         <v>26</v>
       </c>
@@ -34331,7 +34339,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="381" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A381" t="s">
         <v>26</v>
       </c>
@@ -34369,7 +34377,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="382" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A382" t="s">
         <v>26</v>
       </c>
@@ -34407,7 +34415,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="383" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A383" t="s">
         <v>26</v>
       </c>
@@ -34445,7 +34453,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="384" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A384" s="9" t="s">
         <v>26</v>
       </c>
@@ -34482,7 +34490,7 @@
       <c r="L384" s="9"/>
       <c r="M384" s="9"/>
     </row>
-    <row r="385" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A385" s="9" t="s">
         <v>26</v>
       </c>
@@ -34519,7 +34527,7 @@
       <c r="L385" s="9"/>
       <c r="M385" s="9"/>
     </row>
-    <row r="386" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A386" s="9" t="s">
         <v>26</v>
       </c>
@@ -34556,7 +34564,7 @@
       <c r="L386" s="9"/>
       <c r="M386" s="9"/>
     </row>
-    <row r="387" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A387" s="9" t="s">
         <v>26</v>
       </c>
@@ -34591,7 +34599,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="388" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A388" s="9" t="s">
         <v>26</v>
       </c>
@@ -34626,7 +34634,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="389" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A389" s="9" t="s">
         <v>26</v>
       </c>
@@ -34661,7 +34669,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="390" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A390" t="s">
         <v>26</v>
       </c>
@@ -34698,7 +34706,7 @@
       <c r="L390"/>
       <c r="M390"/>
     </row>
-    <row r="391" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A391" t="s">
         <v>26</v>
       </c>
@@ -34735,7 +34743,7 @@
       <c r="L391"/>
       <c r="M391"/>
     </row>
-    <row r="392" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A392" t="s">
         <v>26</v>
       </c>
@@ -34770,7 +34778,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="393" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A393" t="s">
         <v>26</v>
       </c>
@@ -34805,7 +34813,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="394" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A394" t="s">
         <v>26</v>
       </c>
@@ -34834,7 +34842,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="395" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A395" t="s">
         <v>26</v>
       </c>
@@ -34863,7 +34871,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="396" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A396" t="s">
         <v>26</v>
       </c>
@@ -34892,7 +34900,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="397" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A397" t="s">
         <v>26</v>
       </c>
@@ -34921,7 +34929,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="398" spans="1:13" s="15" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:13" s="15" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A398" t="s">
         <v>26</v>
       </c>
@@ -34954,7 +34962,7 @@
       <c r="L398"/>
       <c r="M398"/>
     </row>
-    <row r="399" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A399" t="s">
         <v>26</v>
       </c>
@@ -34983,7 +34991,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="400" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A400" t="s">
         <v>26</v>
       </c>
@@ -35012,7 +35020,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="401" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A401" t="s">
         <v>26</v>
       </c>
@@ -35041,7 +35049,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="402" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A402" t="s">
         <v>26</v>
       </c>
@@ -35074,7 +35082,7 @@
       <c r="L402"/>
       <c r="M402"/>
     </row>
-    <row r="403" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A403" t="s">
         <v>26</v>
       </c>
@@ -35107,7 +35115,7 @@
       <c r="L403"/>
       <c r="M403"/>
     </row>
-    <row r="404" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A404" t="s">
         <v>26</v>
       </c>
@@ -35142,7 +35150,7 @@
       <c r="L404"/>
       <c r="M404"/>
     </row>
-    <row r="405" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A405" s="9" t="s">
         <v>26</v>
       </c>
@@ -35177,7 +35185,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="406" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A406" s="9" t="s">
         <v>26</v>
       </c>
@@ -35212,7 +35220,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="407" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A407" s="9" t="s">
         <v>26</v>
       </c>
@@ -35247,7 +35255,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="408" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A408" s="9" t="s">
         <v>26</v>
       </c>
@@ -35282,7 +35290,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="409" spans="1:13" s="19" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:13" s="19" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A409" s="9" t="s">
         <v>26</v>
       </c>
@@ -35319,7 +35327,7 @@
       <c r="L409" s="9"/>
       <c r="M409" s="9"/>
     </row>
-    <row r="410" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A410" t="s">
         <v>26</v>
       </c>
@@ -35354,7 +35362,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="411" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A411" t="s">
         <v>26</v>
       </c>
@@ -35389,7 +35397,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="412" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A412" t="s">
         <v>26</v>
       </c>
@@ -35424,7 +35432,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="413" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A413" t="s">
         <v>26</v>
       </c>
@@ -35459,7 +35467,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="414" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A414" t="s">
         <v>26</v>
       </c>
@@ -35494,7 +35502,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="415" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A415" s="9" t="s">
         <v>26</v>
       </c>
@@ -35531,7 +35539,7 @@
       <c r="L415" s="9"/>
       <c r="M415" s="9"/>
     </row>
-    <row r="416" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A416" s="9" t="s">
         <v>26</v>
       </c>
@@ -35568,7 +35576,7 @@
       <c r="L416" s="9"/>
       <c r="M416" s="9"/>
     </row>
-    <row r="417" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A417" s="9" t="s">
         <v>26</v>
       </c>
@@ -35605,7 +35613,7 @@
       <c r="L417" s="9"/>
       <c r="M417" s="9"/>
     </row>
-    <row r="418" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A418" s="9" t="s">
         <v>26</v>
       </c>
@@ -35642,7 +35650,7 @@
       <c r="L418" s="9"/>
       <c r="M418" s="9"/>
     </row>
-    <row r="419" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A419" s="9" t="s">
         <v>26</v>
       </c>
@@ -35679,7 +35687,7 @@
       <c r="L419" s="9"/>
       <c r="M419" s="9"/>
     </row>
-    <row r="420" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A420" s="9" t="s">
         <v>26</v>
       </c>
@@ -35716,7 +35724,7 @@
       <c r="L420" s="9"/>
       <c r="M420" s="9"/>
     </row>
-    <row r="421" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A421" s="9" t="s">
         <v>26</v>
       </c>
@@ -35753,7 +35761,7 @@
       <c r="L421" s="9"/>
       <c r="M421" s="9"/>
     </row>
-    <row r="422" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A422" s="9" t="s">
         <v>26</v>
       </c>
@@ -35790,7 +35798,7 @@
       <c r="L422" s="9"/>
       <c r="M422" s="9"/>
     </row>
-    <row r="423" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A423" s="13" t="s">
         <v>26</v>
       </c>
@@ -35827,20 +35835,20 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A7351186-A8CE-4A0C-8910-5842DB016E6F}">
   <dimension ref="A1:I104"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="8.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="46.140625" style="21" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.28515625" style="8" customWidth="1"/>
-    <col min="4" max="4" width="30.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="48.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="69.85546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="46.1796875" style="21" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.26953125" style="8" customWidth="1"/>
+    <col min="4" max="4" width="30.54296875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="48.54296875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="69.81640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.81640625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="12" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="77.85546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="77.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
         <v>13</v>
       </c>
@@ -35869,7 +35877,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>362</v>
       </c>
@@ -35898,7 +35906,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>362</v>
       </c>
@@ -35927,7 +35935,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>362</v>
       </c>
@@ -35956,7 +35964,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>362</v>
       </c>
@@ -35985,7 +35993,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>362</v>
       </c>
@@ -36011,7 +36019,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>362</v>
       </c>
@@ -36037,7 +36045,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>362</v>
       </c>
@@ -36063,7 +36071,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>362</v>
       </c>
@@ -36092,7 +36100,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>362</v>
       </c>
@@ -36121,7 +36129,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>362</v>
       </c>
@@ -36150,7 +36158,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>394</v>
       </c>
@@ -36176,7 +36184,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>394</v>
       </c>
@@ -36205,7 +36213,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>362</v>
       </c>
@@ -36234,7 +36242,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>362</v>
       </c>
@@ -36260,7 +36268,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>362</v>
       </c>
@@ -36289,7 +36297,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>362</v>
       </c>
@@ -36318,7 +36326,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>362</v>
       </c>
@@ -36347,7 +36355,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>394</v>
       </c>
@@ -36376,7 +36384,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>394</v>
       </c>
@@ -36402,7 +36410,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>362</v>
       </c>
@@ -36431,7 +36439,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>362</v>
       </c>
@@ -36460,7 +36468,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>362</v>
       </c>
@@ -36489,7 +36497,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>362</v>
       </c>
@@ -36515,7 +36523,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>362</v>
       </c>
@@ -36541,7 +36549,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>394</v>
       </c>
@@ -36567,7 +36575,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>394</v>
       </c>
@@ -36593,7 +36601,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>394</v>
       </c>
@@ -36619,7 +36627,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>394</v>
       </c>
@@ -36645,7 +36653,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>394</v>
       </c>
@@ -36671,7 +36679,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>394</v>
       </c>
@@ -36700,7 +36708,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>362</v>
       </c>
@@ -36726,7 +36734,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>394</v>
       </c>
@@ -36752,7 +36760,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>394</v>
       </c>
@@ -36781,7 +36789,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>394</v>
       </c>
@@ -36807,7 +36815,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>394</v>
       </c>
@@ -36836,7 +36844,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>394</v>
       </c>
@@ -36862,7 +36870,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>362</v>
       </c>
@@ -36891,7 +36899,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>362</v>
       </c>
@@ -36920,7 +36928,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>394</v>
       </c>
@@ -36946,7 +36954,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>394</v>
       </c>
@@ -36972,7 +36980,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>362</v>
       </c>
@@ -37001,7 +37009,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>362</v>
       </c>
@@ -37030,7 +37038,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>362</v>
       </c>
@@ -37059,7 +37067,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>362</v>
       </c>
@@ -37088,7 +37096,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>362</v>
       </c>
@@ -37117,7 +37125,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>394</v>
       </c>
@@ -37146,7 +37154,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>394</v>
       </c>
@@ -37172,7 +37180,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>362</v>
       </c>
@@ -37201,7 +37209,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>362</v>
       </c>
@@ -37227,7 +37235,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>362</v>
       </c>
@@ -37253,7 +37261,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>362</v>
       </c>
@@ -37279,7 +37287,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>362</v>
       </c>
@@ -37308,7 +37316,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>362</v>
       </c>
@@ -37337,7 +37345,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>362</v>
       </c>
@@ -37363,7 +37371,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>394</v>
       </c>
@@ -37389,7 +37397,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>394</v>
       </c>
@@ -37415,7 +37423,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>362</v>
       </c>
@@ -37441,7 +37449,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>362</v>
       </c>
@@ -37467,7 +37475,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>394</v>
       </c>
@@ -37493,7 +37501,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>394</v>
       </c>
@@ -37519,7 +37527,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>394</v>
       </c>
@@ -37545,7 +37553,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>394</v>
       </c>
@@ -37571,7 +37579,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>362</v>
       </c>
@@ -37597,7 +37605,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>362</v>
       </c>
@@ -37623,7 +37631,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>362</v>
       </c>
@@ -37652,7 +37660,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>362</v>
       </c>
@@ -37681,7 +37689,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>362</v>
       </c>
@@ -37707,7 +37715,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>394</v>
       </c>
@@ -37733,7 +37741,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>394</v>
       </c>
@@ -37759,7 +37767,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>394</v>
       </c>
@@ -37785,7 +37793,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>394</v>
       </c>
@@ -37811,7 +37819,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>362</v>
       </c>
@@ -37840,7 +37848,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>394</v>
       </c>
@@ -37869,7 +37877,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>394</v>
       </c>
@@ -37895,7 +37903,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>362</v>
       </c>
@@ -37921,7 +37929,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
         <v>362</v>
       </c>
@@ -37947,7 +37955,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
         <v>362</v>
       </c>
@@ -37973,7 +37981,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
         <v>394</v>
       </c>
@@ -37999,7 +38007,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
         <v>362</v>
       </c>
@@ -38028,7 +38036,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
         <v>394</v>
       </c>
@@ -38054,7 +38062,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
         <v>394</v>
       </c>
@@ -38080,7 +38088,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
         <v>362</v>
       </c>
@@ -38109,7 +38117,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
         <v>362</v>
       </c>
@@ -38138,7 +38146,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
         <v>362</v>
       </c>
@@ -38167,7 +38175,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
         <v>362</v>
       </c>
@@ -38193,7 +38201,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
         <v>394</v>
       </c>
@@ -38219,7 +38227,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
         <v>362</v>
       </c>
@@ -38248,7 +38256,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
         <v>362</v>
       </c>
@@ -38274,7 +38282,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
         <v>362</v>
       </c>
@@ -38300,7 +38308,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
         <v>362</v>
       </c>
@@ -38329,7 +38337,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
         <v>362</v>
       </c>
@@ -38356,7 +38364,7 @@
       </c>
       <c r="I92" s="23"/>
     </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
         <v>362</v>
       </c>
@@ -38383,7 +38391,7 @@
       </c>
       <c r="I93" s="23"/>
     </row>
-    <row r="94" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
         <v>362</v>
       </c>
@@ -38410,7 +38418,7 @@
       </c>
       <c r="I94" s="23"/>
     </row>
-    <row r="95" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
         <v>362</v>
       </c>
@@ -38437,7 +38445,7 @@
       </c>
       <c r="I95" s="23"/>
     </row>
-    <row r="96" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
         <v>362</v>
       </c>
@@ -38463,7 +38471,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="97" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
         <v>362</v>
       </c>
@@ -38492,7 +38500,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="98" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
         <v>362</v>
       </c>
@@ -38521,7 +38529,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="99" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
         <v>362</v>
       </c>
@@ -38547,7 +38555,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="100" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
         <v>362</v>
       </c>
@@ -38573,7 +38581,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="101" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
         <v>362</v>
       </c>
@@ -38599,7 +38607,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="102" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
         <v>362</v>
       </c>
@@ -38625,7 +38633,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="103" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
         <v>362</v>
       </c>
@@ -38651,7 +38659,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="104" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
         <v>362</v>
       </c>
@@ -38678,6 +38686,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:I1" xr:uid="{A7351186-A8CE-4A0C-8910-5842DB016E6F}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>